--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -514,44 +514,44 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11028</v>
+        <v>7258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10922</v>
+        <v>7174.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 09:45</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11074</v>
+        <v>7334</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00</t>
+          <t>2026-09-10 14:45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.37% (152.0)</t>
+          <t>2.17% (159.5)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11226</v>
+        <v>7493.5</v>
       </c>
       <c r="L2" t="n">
-        <v>11378</v>
+        <v>7653</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -567,53 +567,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>235.84</v>
+        <v>11028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-11 13:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>234.06</v>
+        <v>10922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>236.11</v>
+        <v>11074</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-09 12:45</t>
+          <t>2026-09-10 15:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.87% (2.05)</t>
+          <t>1.37% (152.0)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>238.16</v>
+        <v>11226</v>
       </c>
       <c r="L3" t="n">
-        <v>240.21</v>
+        <v>11378</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -629,53 +629,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>402.9</v>
+        <v>235.84</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-10 09:15</t>
+          <t>2026-09-08 11:45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15</t>
+          <t>2026-09-11 10:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>399.75</v>
+        <v>234.06</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-09 15:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>405</v>
+        <v>236.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-09 12:45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.3% (5.25)</t>
+          <t>0.87% (2.05)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>410.25</v>
+        <v>238.16</v>
       </c>
       <c r="L4" t="n">
-        <v>415.5</v>
+        <v>240.21</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -700,20 +700,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1151</v>
+        <v>402.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-10 09:15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11 10:45</t>
+          <t>2026-09-11 11:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1132</v>
+        <v>399.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -721,23 +721,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1152.6</v>
+        <v>405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:45</t>
+          <t>2026-09-10 15:15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.79% (20.6)</t>
+          <t>1.3% (5.25)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1173.2</v>
+        <v>410.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1193.8</v>
+        <v>415.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -753,16 +753,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>859.55</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -771,35 +771,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 10:45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>855.45</v>
+        <v>1132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>864.85</v>
+        <v>1152.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-08 14:45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.09% (9.4)</t>
+          <t>1.79% (20.6)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>874.25</v>
+        <v>1173.2</v>
       </c>
       <c r="L6" t="n">
-        <v>883.65</v>
+        <v>1193.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -815,53 +815,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>698.5</v>
+        <v>859.55</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>682.1</v>
+        <v>855.45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 09:30</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>704.55</v>
+        <v>864.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.19% (22.45)</t>
+          <t>1.09% (9.4)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>727</v>
+        <v>874.25</v>
       </c>
       <c r="L7" t="n">
-        <v>749.45</v>
+        <v>883.65</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -886,11 +886,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4908.5</v>
+        <v>698.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-10 09:30</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4822</v>
+        <v>682.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -907,23 +907,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4945</v>
+        <v>704.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-08 15:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.49% (123.0)</t>
+          <t>3.19% (22.45)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5068</v>
+        <v>727</v>
       </c>
       <c r="L8" t="n">
-        <v>5191</v>
+        <v>749.45</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -939,53 +939,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>134.32</v>
+        <v>4908.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-08 12:15</t>
+          <t>2026-09-10 09:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11 12:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>133.11</v>
+        <v>4822</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>134.45</v>
+        <v>4945</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:15</t>
+          <t>2026-09-10 15:15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.0% (1.34)</t>
+          <t>2.49% (123.0)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>135.79</v>
+        <v>5068</v>
       </c>
       <c r="L9" t="n">
-        <v>137.13</v>
+        <v>5191</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1001,53 +1001,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>418.95</v>
+        <v>134.32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 12:15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-11 12:15</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>409.25</v>
+        <v>133.11</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 13:45</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>420.45</v>
+        <v>134.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 13:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.66% (11.2)</t>
+          <t>1.0% (1.34)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>431.65</v>
+        <v>135.79</v>
       </c>
       <c r="L10" t="n">
-        <v>442.85</v>
+        <v>137.13</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1072,44 +1072,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1026.1</v>
+        <v>418.95</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1013.3</v>
+        <v>409.25</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-11 09:30</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1038</v>
+        <v>420.45</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.38% (24.7)</t>
+          <t>2.66% (11.2)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1062.7</v>
+        <v>431.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1087.4</v>
+        <v>442.85</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,28 +1134,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.4</v>
+        <v>1026.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>180.86</v>
+        <v>1013.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 09:30</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>186.78</v>
+        <v>1038</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1164,14 +1164,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.17% (5.92)</t>
+          <t>2.38% (24.7)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>192.7</v>
+        <v>1062.7</v>
       </c>
       <c r="L12" t="n">
-        <v>198.62</v>
+        <v>1087.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1187,60 +1187,122 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>180.86</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>186.78</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3.17% (5.92)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>192.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>198.62</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>4952</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>2026-09-11 09:45</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>4945</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>5021</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-09-10 15:15</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1.51% (76.0)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>5097</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>5173</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1257,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,7 +1397,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1344,44 +1406,44 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11028</v>
+        <v>7258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10922</v>
+        <v>7174.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 09:45</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11074</v>
+        <v>7334</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00</t>
+          <t>2026-09-10 14:45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.37% (152.0)</t>
+          <t>2.17% (159.5)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11226</v>
+        <v>7493.5</v>
       </c>
       <c r="L2" t="n">
-        <v>11378</v>
+        <v>7653</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1397,53 +1459,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>235.84</v>
+        <v>11028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-11 13:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>234.06</v>
+        <v>10922</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>236.11</v>
+        <v>11074</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-09 12:45</t>
+          <t>2026-09-10 15:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.87% (2.05)</t>
+          <t>1.37% (152.0)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>238.16</v>
+        <v>11226</v>
       </c>
       <c r="L3" t="n">
-        <v>240.21</v>
+        <v>11378</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1459,53 +1521,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>402.9</v>
+        <v>235.84</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-10 09:15</t>
+          <t>2026-09-08 11:45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15</t>
+          <t>2026-09-11 10:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>399.75</v>
+        <v>234.06</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-09 15:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>405</v>
+        <v>236.11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-09 12:45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.3% (5.25)</t>
+          <t>0.87% (2.05)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>410.25</v>
+        <v>238.16</v>
       </c>
       <c r="L4" t="n">
-        <v>415.5</v>
+        <v>240.21</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1521,7 +1583,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1530,20 +1592,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1151</v>
+        <v>402.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-10 09:15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11 10:45</t>
+          <t>2026-09-11 11:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1132</v>
+        <v>399.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1551,23 +1613,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1152.6</v>
+        <v>405</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-08 14:45</t>
+          <t>2026-09-10 15:15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.79% (20.6)</t>
+          <t>1.3% (5.25)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1173.2</v>
+        <v>410.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1193.8</v>
+        <v>415.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1583,16 +1645,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>859.55</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1601,35 +1663,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 10:45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>855.45</v>
+        <v>1132</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>864.85</v>
+        <v>1152.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-08 14:45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.09% (9.4)</t>
+          <t>1.79% (20.6)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>874.25</v>
+        <v>1173.2</v>
       </c>
       <c r="L6" t="n">
-        <v>883.65</v>
+        <v>1193.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1645,53 +1707,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>698.5</v>
+        <v>859.55</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>682.1</v>
+        <v>855.45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 09:30</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>704.55</v>
+        <v>864.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.19% (22.45)</t>
+          <t>1.09% (9.4)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>727</v>
+        <v>874.25</v>
       </c>
       <c r="L7" t="n">
-        <v>749.45</v>
+        <v>883.65</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1707,7 +1769,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1716,11 +1778,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4908.5</v>
+        <v>698.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-10 09:30</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1729,7 +1791,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4822</v>
+        <v>682.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1737,23 +1799,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4945</v>
+        <v>704.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-08 15:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.49% (123.0)</t>
+          <t>3.19% (22.45)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>5068</v>
+        <v>727</v>
       </c>
       <c r="L8" t="n">
-        <v>5191</v>
+        <v>749.45</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1769,53 +1831,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>134.32</v>
+        <v>4908.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-08 12:15</t>
+          <t>2026-09-10 09:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11 12:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>133.11</v>
+        <v>4822</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:45</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>134.45</v>
+        <v>4945</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-08 13:15</t>
+          <t>2026-09-10 15:15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.0% (1.34)</t>
+          <t>2.49% (123.0)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>135.79</v>
+        <v>5068</v>
       </c>
       <c r="L9" t="n">
-        <v>137.13</v>
+        <v>5191</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1831,53 +1893,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>418.95</v>
+        <v>134.32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 12:15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-11 12:15</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>409.25</v>
+        <v>133.11</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 13:45</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>420.45</v>
+        <v>134.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-08 13:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.66% (11.2)</t>
+          <t>1.0% (1.34)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>431.65</v>
+        <v>135.79</v>
       </c>
       <c r="L10" t="n">
-        <v>442.85</v>
+        <v>137.13</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1893,7 +1955,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1902,44 +1964,44 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1026.1</v>
+        <v>418.95</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-11 15:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1013.3</v>
+        <v>409.25</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-11 09:30</t>
+          <t>2026-09-11 09:15</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1038</v>
+        <v>420.45</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-09 09:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.38% (24.7)</t>
+          <t>2.66% (11.2)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1062.7</v>
+        <v>431.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1087.4</v>
+        <v>442.85</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1955,7 +2017,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1964,28 +2026,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.4</v>
+        <v>1026.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-08 09:15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 13:45</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>180.86</v>
+        <v>1013.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-11 09:30</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>186.78</v>
+        <v>1038</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1994,14 +2056,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.17% (5.92)</t>
+          <t>2.38% (24.7)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>192.7</v>
+        <v>1062.7</v>
       </c>
       <c r="L12" t="n">
-        <v>198.62</v>
+        <v>1087.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2017,60 +2079,122 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>180.86</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>186.78</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3.17% (5.92)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>192.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>198.62</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>TITAN</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>4952</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>2026-09-11 09:45</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" t="n">
         <v>4945</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>5021</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>2026-09-10 15:15</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1.51% (76.0)</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
         <v>5097</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>5173</v>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,53 +505,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7258</v>
+        <v>1832.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 11:45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7174.5</v>
+        <v>1824</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:45</t>
+          <t>2026-09-22 14:00</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7334</v>
+        <v>1835.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:45</t>
+          <t>2026-09-22 13:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.17% (159.5)</t>
+          <t>0.64% (11.7)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7493.5</v>
+        <v>1847.4</v>
       </c>
       <c r="L2" t="n">
-        <v>7653</v>
+        <v>1859.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -567,53 +567,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11028</v>
+        <v>1818.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10922</v>
+        <v>1813</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 14:00</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11074</v>
+        <v>1832.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00</t>
+          <t>2026-09-22 11:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.37% (152.0)</t>
+          <t>1.08% (19.8)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11226</v>
+        <v>1852.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11378</v>
+        <v>1872.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -629,53 +629,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235.84</v>
+        <v>3159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>234.06</v>
+        <v>3125</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>236.11</v>
+        <v>3176.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:45</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.87% (2.05)</t>
+          <t>1.63% (51.9)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>238.16</v>
+        <v>3228.8</v>
       </c>
       <c r="L4" t="n">
-        <v>240.21</v>
+        <v>3280.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -691,53 +691,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>402.9</v>
+        <v>1338.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-10 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>399.75</v>
+        <v>1331.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>405</v>
+        <v>1342.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-23 14:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.3% (5.25)</t>
+          <t>0.82% (11.0)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>410.25</v>
+        <v>1353.3</v>
       </c>
       <c r="L5" t="n">
-        <v>415.5</v>
+        <v>1364.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -753,53 +753,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1151</v>
+        <v>3029.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-23 09:45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11 10:45</t>
+          <t>2026-09-23 14:45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1132</v>
+        <v>3022.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-23 10:00</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1152.6</v>
+        <v>3062.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:45</t>
+          <t>2026-09-22 14:30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.79% (20.6)</t>
+          <t>1.3% (39.7)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1173.2</v>
+        <v>3101.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1193.8</v>
+        <v>3141.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -815,53 +815,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>859.55</v>
+        <v>308.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>855.45</v>
+        <v>307.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>864.85</v>
+        <v>308.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.09% (9.4)</t>
+          <t>0.57% (1.75)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>874.25</v>
+        <v>310.6</v>
       </c>
       <c r="L7" t="n">
-        <v>883.65</v>
+        <v>312.35</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -877,53 +877,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>698.5</v>
+        <v>986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-23 10:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>682.1</v>
+        <v>984.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>704.55</v>
+        <v>991</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.19% (22.45)</t>
+          <t>0.7% (6.9)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>727</v>
+        <v>997.9</v>
       </c>
       <c r="L8" t="n">
-        <v>749.45</v>
+        <v>1004.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -939,53 +939,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4908.5</v>
+        <v>299.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-10 09:30</t>
+          <t>2026-09-21 10:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4822</v>
+        <v>298.65</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4945</v>
+        <v>301.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.49% (123.0)</t>
+          <t>0.91% (2.75)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5068</v>
+        <v>304.15</v>
       </c>
       <c r="L9" t="n">
-        <v>5191</v>
+        <v>306.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -993,316 +993,6 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>134.32</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-08 12:15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:15</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>133.11</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-09-08 13:45</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>134.45</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-09-08 13:15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.0% (1.34)</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>135.79</v>
-      </c>
-      <c r="L10" t="n">
-        <v>137.13</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>418.95</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>409.25</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>420.45</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.66% (11.2)</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>431.65</v>
-      </c>
-      <c r="L11" t="n">
-        <v>442.85</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1026.1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:45</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1013.3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:30</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1038</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2.38% (24.7)</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1062.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1087.4</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>180.86</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>186.78</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3.17% (5.92)</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>192.7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>198.62</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4952</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:45</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>4945</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>5021</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1.51% (76.0)</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5097</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5173</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1319,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,53 +1087,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7258</v>
+        <v>1832.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 11:45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7174.5</v>
+        <v>1824</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 09:45</t>
+          <t>2026-09-22 14:00</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>7334</v>
+        <v>1835.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:45</t>
+          <t>2026-09-22 13:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.17% (159.5)</t>
+          <t>0.64% (11.7)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7493.5</v>
+        <v>1847.4</v>
       </c>
       <c r="L2" t="n">
-        <v>7653</v>
+        <v>1859.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1459,53 +1149,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11028</v>
+        <v>1818.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11 13:00</t>
+          <t>2026-09-23 09:15</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10922</v>
+        <v>1813</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 14:00</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11074</v>
+        <v>1832.8</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-10 15:00</t>
+          <t>2026-09-22 11:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.37% (152.0)</t>
+          <t>1.08% (19.8)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>11226</v>
+        <v>1852.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11378</v>
+        <v>1872.4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1521,53 +1211,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235.84</v>
+        <v>3159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:45</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11 10:00</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>234.06</v>
+        <v>3125</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:00</t>
+          <t>2026-09-22 13:00</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>236.11</v>
+        <v>3176.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:45</t>
+          <t>2026-09-22 09:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.87% (2.05)</t>
+          <t>1.63% (51.9)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>238.16</v>
+        <v>3228.8</v>
       </c>
       <c r="L4" t="n">
-        <v>240.21</v>
+        <v>3280.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1583,53 +1273,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>402.9</v>
+        <v>1338.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-10 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>399.75</v>
+        <v>1331.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>405</v>
+        <v>1342.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-23 14:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.3% (5.25)</t>
+          <t>0.82% (11.0)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>410.25</v>
+        <v>1353.3</v>
       </c>
       <c r="L5" t="n">
-        <v>415.5</v>
+        <v>1364.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1645,53 +1335,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1151</v>
+        <v>3029.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-23 09:45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-11 10:45</t>
+          <t>2026-09-23 14:45</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1132</v>
+        <v>3022.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-23 10:00</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1152.6</v>
+        <v>3062.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-08 14:45</t>
+          <t>2026-09-22 14:30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.79% (20.6)</t>
+          <t>1.3% (39.7)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1173.2</v>
+        <v>3101.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1193.8</v>
+        <v>3141.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1707,53 +1397,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>859.55</v>
+        <v>308.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 10:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>855.45</v>
+        <v>307.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>864.85</v>
+        <v>308.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-08 09:15</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.09% (9.4)</t>
+          <t>0.57% (1.75)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>874.25</v>
+        <v>310.6</v>
       </c>
       <c r="L7" t="n">
-        <v>883.65</v>
+        <v>312.35</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1769,53 +1459,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>698.5</v>
+        <v>986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-23 10:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>682.1</v>
+        <v>984.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-22 15:15</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>704.55</v>
+        <v>991</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-08 15:00</t>
+          <t>2026-09-22 14:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.19% (22.45)</t>
+          <t>0.7% (6.9)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>727</v>
+        <v>997.9</v>
       </c>
       <c r="L8" t="n">
-        <v>749.45</v>
+        <v>1004.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1831,53 +1521,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4908.5</v>
+        <v>299.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-10 09:30</t>
+          <t>2026-09-21 10:30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-11 13:45</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4822</v>
+        <v>298.65</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-11 09:15</t>
+          <t>2026-09-24 09:15</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4945</v>
+        <v>301.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:15</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.49% (123.0)</t>
+          <t>0.91% (2.75)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>5068</v>
+        <v>304.15</v>
       </c>
       <c r="L9" t="n">
-        <v>5191</v>
+        <v>306.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1885,316 +1575,6 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>IOC</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>134.32</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-08 12:15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:15</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>133.11</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-09-08 13:45</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>134.45</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-09-08 13:15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1.0% (1.34)</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>135.79</v>
-      </c>
-      <c r="L10" t="n">
-        <v>137.13</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>418.95</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:00</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>409.25</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>420.45</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-09-09 09:15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.66% (11.2)</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>431.65</v>
-      </c>
-      <c r="L11" t="n">
-        <v>442.85</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1026.1</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-09-08 09:15</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:45</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1013.3</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:30</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1038</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2.38% (24.7)</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>1062.7</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1087.4</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>180.86</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>186.78</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3.17% (5.92)</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>192.7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>198.62</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>4952</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:45</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>4945</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:15</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>5021</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1.51% (76.0)</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>5097</v>
-      </c>
-      <c r="L14" t="n">
-        <v>5173</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -833,7 +833,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="F8" t="n">

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -709,7 +709,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -895,7 +895,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 10:00</t>
         </is>
       </c>
       <c r="F9" t="n">

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -709,35 +709,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 14:45</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1331.3</v>
+        <v>1330.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1342.3</v>
+        <v>1347.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.82% (11.0)</t>
+          <t>1.31% (17.6)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1353.3</v>
+        <v>1365.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1364.3</v>
+        <v>1383</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -771,35 +771,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-23 14:45</t>
+          <t>2026-09-24 11:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3022.4</v>
+        <v>3009.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3062.1</v>
+        <v>3041.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:30</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.3% (39.7)</t>
+          <t>1.06% (32.1)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3101.8</v>
+        <v>3073.6</v>
       </c>
       <c r="L6" t="n">
-        <v>3141.5</v>
+        <v>3105.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-24 12:15</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -895,35 +895,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-24 14:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>984.1</v>
+        <v>983</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-24 11:00</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-24 10:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.7% (6.9)</t>
+          <t>0.51% (5.0)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>997.9</v>
+        <v>993</v>
       </c>
       <c r="L8" t="n">
-        <v>1004.8</v>
+        <v>998</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 11:45</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-23 09:15</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1291,35 +1291,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 14:45</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1331.3</v>
+        <v>1330.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-24 11:30</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1342.3</v>
+        <v>1347.8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-23 14:00</t>
+          <t>2026-09-24 09:30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.82% (11.0)</t>
+          <t>1.31% (17.6)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1353.3</v>
+        <v>1365.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1364.3</v>
+        <v>1383</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1353,35 +1353,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-23 14:45</t>
+          <t>2026-09-24 11:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3022.4</v>
+        <v>3009.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-23 10:00</t>
+          <t>2026-09-24 09:45</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3062.1</v>
+        <v>3041.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-22 14:30</t>
+          <t>2026-09-23 15:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.3% (39.7)</t>
+          <t>1.06% (32.1)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3101.8</v>
+        <v>3073.6</v>
       </c>
       <c r="L6" t="n">
-        <v>3141.5</v>
+        <v>3105.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-24 12:15</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1477,35 +1477,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-24 14:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>984.1</v>
+        <v>983</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-24 11:00</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-24 10:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.7% (6.9)</t>
+          <t>0.51% (5.0)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>997.9</v>
+        <v>993</v>
       </c>
       <c r="L8" t="n">
-        <v>1004.8</v>
+        <v>998</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 10:00</t>
+          <t>2026-09-24 11:45</t>
         </is>
       </c>
       <c r="F9" t="n">

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-24 15:15</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-24 15:15</t>
         </is>
       </c>
       <c r="F8" t="n">

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,378 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1335.9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1347.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.84% (11.3)</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>565.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9.05% (51.15)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>616.55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>667.7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:30</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1935.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.52% (10.1)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1945.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1955.8</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>456.95</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>446.15</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>485</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8.01% (38.85)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>523.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>472</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:45</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>463.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:15</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3.74% (18.0)</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1521.1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1558.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.63% (41.0)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1599.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1640.5</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1009,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1947,378 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1336.5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1335.9</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1347.2</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.84% (11.3)</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1358.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1369.8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>516.1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>565.4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9.05% (51.15)</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>616.55</v>
+      </c>
+      <c r="L11" t="n">
+        <v>667.7</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1927</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:30</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1925.5</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1935.6</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.52% (10.1)</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1945.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1955.8</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>456.95</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:30</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>446.15</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>485</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-23 15:00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8.01% (38.85)</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>523.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>472</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-09-22 09:15</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:45</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>463.7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:15</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>481.7</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3.74% (18.0)</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>499.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1521.1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:00</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1517.5</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1558.5</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-24 10:30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.63% (41.0)</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1599.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1640.5</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,7 +758,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -771,35 +771,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:00</t>
+          <t>2026-09-25 14:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3009.4</v>
+        <v>2967.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3041.5</v>
+        <v>3039</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-24 11:15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.06% (32.1)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3073.6</v>
+        <v>3110.9</v>
       </c>
       <c r="L6" t="n">
-        <v>3105.7</v>
+        <v>3182.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 12:15</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -895,15 +895,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15</t>
+          <t>2026-09-25 10:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>983</v>
+        <v>982.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-24 11:00</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -911,19 +911,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:30</t>
+          <t>2026-09-24 14:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.51% (5.0)</t>
+          <t>0.53% (5.2)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>993</v>
+        <v>993.2</v>
       </c>
       <c r="L8" t="n">
-        <v>998</v>
+        <v>998.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1019,35 +1019,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-25 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1335.9</v>
+        <v>1315</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1347.2</v>
+        <v>1343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.84% (11.3)</t>
+          <t>2.08% (28.0)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1358.5</v>
+        <v>1371</v>
       </c>
       <c r="L10" t="n">
-        <v>1369.8</v>
+        <v>1399</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1143,35 +1143,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-25 13:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1925.5</v>
+        <v>1915.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-24 14:00</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1935.6</v>
+        <v>1935.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.52% (10.1)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1945.7</v>
+        <v>1955.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1955.8</v>
+        <v>1975.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-24 12:45</t>
+          <t>2026-09-25 12:45</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1365,6 +1365,440 @@
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2907</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:15</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2945.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.61% (47.5)</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>2993.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3040.7</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:15</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:45</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>203.34</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.56% (7.24)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="L17" t="n">
+        <v>217.82</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1219.9</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1175.1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:15</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1247.4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.8% (72.3)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1392</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10821.29</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:15</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10746</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>11023</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2.51% (277.0)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>11300</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11577</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4933</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4883.5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:45</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4936</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.06% (52.5)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>4988.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5041</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:45</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1246</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.48% (43.4)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1289.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1332.8</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.93% (3.18)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>168.03</v>
+      </c>
+      <c r="L22" t="n">
+        <v>171.21</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1381,7 +1815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1712,7 +2146,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1725,35 +2159,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:00</t>
+          <t>2026-09-25 14:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3009.4</v>
+        <v>2967.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-24 09:45</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3041.5</v>
+        <v>3039</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-24 11:15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.06% (32.1)</t>
+          <t>2.37% (71.9)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3073.6</v>
+        <v>3110.9</v>
       </c>
       <c r="L6" t="n">
-        <v>3105.7</v>
+        <v>3182.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1787,7 +2221,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-24 12:15</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1836,7 +2270,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1849,15 +2283,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-24 15:15</t>
+          <t>2026-09-25 10:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>983</v>
+        <v>982.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-24 11:00</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1865,19 +2299,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-24 10:30</t>
+          <t>2026-09-24 14:30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.51% (5.0)</t>
+          <t>0.53% (5.2)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>993</v>
+        <v>993.2</v>
       </c>
       <c r="L8" t="n">
-        <v>998</v>
+        <v>998.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1960,7 +2394,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1973,35 +2407,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-25 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1335.9</v>
+        <v>1315</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1347.2</v>
+        <v>1343</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.84% (11.3)</t>
+          <t>2.08% (28.0)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1358.5</v>
+        <v>1371</v>
       </c>
       <c r="L10" t="n">
-        <v>1369.8</v>
+        <v>1399</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2084,7 +2518,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2097,35 +2531,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-25 13:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1925.5</v>
+        <v>1915.1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-24 14:00</t>
+          <t>2026-09-25 09:45</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1935.6</v>
+        <v>1935.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-25 09:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.52% (10.1)</t>
+          <t>1.03% (20.0)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1945.7</v>
+        <v>1955.1</v>
       </c>
       <c r="L12" t="n">
-        <v>1955.8</v>
+        <v>1975.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2221,7 +2655,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-24 12:45</t>
+          <t>2026-09-25 12:45</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2319,6 +2753,440 @@
         </is>
       </c>
       <c r="N15" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2907</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:45</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:15</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2945.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.61% (47.5)</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>2993.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3040.7</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>200.4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:15</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:45</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>203.34</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-24 11:15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.56% (7.24)</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="L17" t="n">
+        <v>217.82</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1219.9</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:00</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1175.1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:15</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1247.4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-23 14:15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.8% (72.3)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1392</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10821.29</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:15</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10746</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>11023</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2.51% (277.0)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>11300</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11577</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4933</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-25 15:15</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4883.5</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:45</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>4936</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.06% (52.5)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>4988.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>5041</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1242.8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-24 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:45</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1202.6</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:00</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1246</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:15</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.48% (43.4)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1289.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1332.8</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-22 10:30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:15</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.93% (3.18)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>168.03</v>
+      </c>
+      <c r="L22" t="n">
+        <v>171.21</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,53 +505,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1832.1</v>
+        <v>196.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22 11:45</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1824</v>
+        <v>195.37</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1835.7</v>
+        <v>197.36</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:30</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>1.01% (1.99)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1847.4</v>
+        <v>199.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1859.1</v>
+        <v>201.34</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -567,53 +567,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1818.6</v>
+        <v>8821.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1813</v>
+        <v>8804.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1832.8</v>
+        <v>8893</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-22 11:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1852.6</v>
+        <v>8981.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1872.4</v>
+        <v>9070</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -629,53 +629,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3159</v>
+        <v>411.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3125</v>
+        <v>407.35</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-28 12:45</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3176.9</v>
+        <v>416.55</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.63% (51.9)</t>
+          <t>2.21% (9.2)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3228.8</v>
+        <v>425.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3280.7</v>
+        <v>434.95</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -691,53 +691,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1338.9</v>
+        <v>4883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 14:45</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1330.2</v>
+        <v>4869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1347.8</v>
+        <v>4902.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 09:45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.31% (17.6)</t>
+          <t>0.68% (33.5)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1365.4</v>
+        <v>4936</v>
       </c>
       <c r="L5" t="n">
-        <v>1383</v>
+        <v>4969.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -753,53 +753,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3029.5</v>
+        <v>1629.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2967.1</v>
+        <v>1621</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3039</v>
+        <v>1660.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>2.37% (39.4)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3110.9</v>
+        <v>1699.8</v>
       </c>
       <c r="L6" t="n">
-        <v>3182.8</v>
+        <v>1739.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -815,53 +815,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>308.5</v>
+        <v>1835.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>307.1</v>
+        <v>1827</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>308.85</v>
+        <v>1857.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.57% (1.75)</t>
+          <t>1.66% (30.9)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>310.6</v>
+        <v>1888.8</v>
       </c>
       <c r="L7" t="n">
-        <v>312.35</v>
+        <v>1919.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -877,53 +877,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>986</v>
+        <v>171.35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>982.8</v>
+        <v>171.05</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 10:30</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>988</v>
+        <v>172.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.53% (5.2)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>993.2</v>
+        <v>173.35</v>
       </c>
       <c r="L8" t="n">
-        <v>998.4</v>
+        <v>174.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -939,53 +939,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>299.3</v>
+        <v>864.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:45</t>
+          <t>2026-09-28 11:45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>298.65</v>
+        <v>859.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>301.4</v>
+        <v>864.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.91% (2.75)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>304.15</v>
+        <v>869.9</v>
       </c>
       <c r="L9" t="n">
-        <v>306.9</v>
+        <v>875</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1001,53 +1001,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1336.5</v>
+        <v>906.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1315</v>
+        <v>889.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 11:00</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1343</v>
+        <v>907.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.08% (28.0)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1371</v>
+        <v>925.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1399</v>
+        <v>943.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1063,53 +1063,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>516.1</v>
+        <v>991.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 11:15</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>514.25</v>
+        <v>986.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 10:30</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>565.4</v>
+        <v>993.4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.05% (51.15)</t>
+          <t>0.68% (6.8)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>616.55</v>
+        <v>1000.2</v>
       </c>
       <c r="L11" t="n">
-        <v>667.7</v>
+        <v>1007</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1125,53 +1125,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1927</v>
+        <v>399.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-25 13:30</t>
+          <t>2026-09-28 12:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1915.1</v>
+        <v>396</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1935.1</v>
+        <v>402</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>1.49% (6.0)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1955.1</v>
+        <v>408</v>
       </c>
       <c r="L12" t="n">
-        <v>1975.1</v>
+        <v>414</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1187,53 +1187,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>456.95</v>
+        <v>11975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 11:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 12:15</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>446.15</v>
+        <v>11945</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 11:45</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>485</v>
+        <v>12020</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.01% (38.85)</t>
+          <t>0.62% (75.0)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>523.85</v>
+        <v>12095</v>
       </c>
       <c r="L13" t="n">
-        <v>562.7</v>
+        <v>12170</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1249,53 +1249,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>472</v>
+        <v>1495.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-25 12:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>463.7</v>
+        <v>1487.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-22 11:15</t>
+          <t>2026-09-28 11:15</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>481.7</v>
+        <v>1498</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-21 14:30</t>
+          <t>2026-09-28 10:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.74% (18.0)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>499.7</v>
+        <v>1508.9</v>
       </c>
       <c r="L14" t="n">
-        <v>517.7</v>
+        <v>1519.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1311,53 +1311,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1521.1</v>
+        <v>22165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-24 14:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1517.5</v>
+        <v>22070</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1558.5</v>
+        <v>22190</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-24 10:30</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.63% (41.0)</t>
+          <t>0.54% (120.0)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1599.5</v>
+        <v>22310</v>
       </c>
       <c r="L15" t="n">
-        <v>1640.5</v>
+        <v>22430</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1373,53 +1373,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2907</v>
+        <v>1650.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-25 13:15</t>
+          <t>2026-09-28 15:15</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2898.2</v>
+        <v>1637</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-24 14:15</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2945.7</v>
+        <v>1661.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.61% (47.5)</t>
+          <t>1.46% (24.2)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2993.2</v>
+        <v>1685.4</v>
       </c>
       <c r="L16" t="n">
-        <v>3040.7</v>
+        <v>1709.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1435,53 +1435,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200.4</v>
+        <v>10983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:15</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>196.1</v>
+        <v>10981</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>203.34</v>
+        <v>11042</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-24 11:15</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>0.55% (61.0)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>210.58</v>
+        <v>11103</v>
       </c>
       <c r="L17" t="n">
-        <v>217.82</v>
+        <v>11164</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1489,316 +1489,6 @@
         </is>
       </c>
       <c r="N17" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1219.9</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1175.1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-09-24 14:15</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1247.4</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5.8% (72.3)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1319.7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1392</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>10821.29</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:30</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:15</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>10746</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:00</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>11023</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2.51% (277.0)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>11300</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11577</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4933</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-22 12:30</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:15</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>4883.5</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:45</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>4936</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1.06% (52.5)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>4988.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5041</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1242.8</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:45</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1202.6</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:00</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1246</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.48% (43.4)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1289.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1332.8</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:30</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:15</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>161.67</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:15</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>164.85</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1.93% (3.18)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>168.03</v>
-      </c>
-      <c r="L22" t="n">
-        <v>171.21</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1815,7 +1505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,53 +1583,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1832.1</v>
+        <v>196.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-22 11:45</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1824</v>
+        <v>195.37</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1835.7</v>
+        <v>197.36</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-22 13:30</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>1.01% (1.99)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1847.4</v>
+        <v>199.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1859.1</v>
+        <v>201.34</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1955,53 +1645,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1818.6</v>
+        <v>8821.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1813</v>
+        <v>8804.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-22 14:00</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1832.8</v>
+        <v>8893</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-22 11:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.08% (19.8)</t>
+          <t>1.0% (88.5)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1852.6</v>
+        <v>8981.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1872.4</v>
+        <v>9070</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -2017,53 +1707,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3159</v>
+        <v>411.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3125</v>
+        <v>407.35</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:00</t>
+          <t>2026-09-28 12:45</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3176.9</v>
+        <v>416.55</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.63% (51.9)</t>
+          <t>2.21% (9.2)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3228.8</v>
+        <v>425.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3280.7</v>
+        <v>434.95</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -2079,53 +1769,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1338.9</v>
+        <v>4883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-24 14:45</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1330.2</v>
+        <v>4869</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-24 11:30</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1347.8</v>
+        <v>4902.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 09:45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.31% (17.6)</t>
+          <t>0.68% (33.5)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1365.4</v>
+        <v>4936</v>
       </c>
       <c r="L5" t="n">
-        <v>1383</v>
+        <v>4969.5</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -2141,53 +1831,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3029.5</v>
+        <v>1629.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-23 09:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-25 14:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2967.1</v>
+        <v>1621</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3039</v>
+        <v>1660.4</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-24 11:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.37% (71.9)</t>
+          <t>2.37% (39.4)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3110.9</v>
+        <v>1699.8</v>
       </c>
       <c r="L6" t="n">
-        <v>3182.8</v>
+        <v>1739.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2203,53 +1893,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>308.5</v>
+        <v>1835.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22 10:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>307.1</v>
+        <v>1827</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>308.85</v>
+        <v>1857.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-22 14:15</t>
+          <t>2026-09-28 13:15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.57% (1.75)</t>
+          <t>1.66% (30.9)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>310.6</v>
+        <v>1888.8</v>
       </c>
       <c r="L7" t="n">
-        <v>312.35</v>
+        <v>1919.7</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2265,53 +1955,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>986</v>
+        <v>171.35</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-22 15:15</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-25 10:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>982.8</v>
+        <v>171.05</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 10:30</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>988</v>
+        <v>172.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-24 14:30</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.53% (5.2)</t>
+          <t>0.67% (1.15)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>993.2</v>
+        <v>173.35</v>
       </c>
       <c r="L8" t="n">
-        <v>998.4</v>
+        <v>174.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2327,53 +2017,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>299.3</v>
+        <v>864.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-21 10:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-24 11:45</t>
+          <t>2026-09-28 11:45</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>298.65</v>
+        <v>859.7</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>301.4</v>
+        <v>864.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.91% (2.75)</t>
+          <t>0.59% (5.1)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>304.15</v>
+        <v>869.9</v>
       </c>
       <c r="L9" t="n">
-        <v>306.9</v>
+        <v>875</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2389,53 +2079,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1336.5</v>
+        <v>906.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-24 15:00</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-25 15:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1315</v>
+        <v>889.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 11:00</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1343</v>
+        <v>907.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.08% (28.0)</t>
+          <t>1.96% (17.8)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1371</v>
+        <v>925.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1399</v>
+        <v>943.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2451,53 +2141,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>516.1</v>
+        <v>991.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 11:15</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>514.25</v>
+        <v>986.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 10:30</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>565.4</v>
+        <v>993.4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-23 14:15</t>
+          <t>2026-09-28 10:15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.05% (51.15)</t>
+          <t>0.68% (6.8)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>616.55</v>
+        <v>1000.2</v>
       </c>
       <c r="L11" t="n">
-        <v>667.7</v>
+        <v>1007</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2513,53 +2203,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1927</v>
+        <v>399.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-25 13:30</t>
+          <t>2026-09-28 12:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1915.1</v>
+        <v>396</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1935.1</v>
+        <v>402</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-25 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.03% (20.0)</t>
+          <t>1.49% (6.0)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1955.1</v>
+        <v>408</v>
       </c>
       <c r="L12" t="n">
-        <v>1975.1</v>
+        <v>414</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2575,53 +2265,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>456.95</v>
+        <v>11975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 11:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:30</t>
+          <t>2026-09-28 12:15</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>446.15</v>
+        <v>11945</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:15</t>
+          <t>2026-09-28 11:45</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>485</v>
+        <v>12020</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-23 15:00</t>
+          <t>2026-09-28 10:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.01% (38.85)</t>
+          <t>0.62% (75.0)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>523.85</v>
+        <v>12095</v>
       </c>
       <c r="L13" t="n">
-        <v>562.7</v>
+        <v>12170</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2637,53 +2327,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>472</v>
+        <v>1495.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-22 09:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-25 12:45</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>463.7</v>
+        <v>1487.1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-22 11:15</t>
+          <t>2026-09-28 11:15</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>481.7</v>
+        <v>1498</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-21 14:30</t>
+          <t>2026-09-28 10:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.74% (18.0)</t>
+          <t>0.73% (10.9)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>499.7</v>
+        <v>1508.9</v>
       </c>
       <c r="L14" t="n">
-        <v>517.7</v>
+        <v>1519.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2699,53 +2389,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1521.1</v>
+        <v>22165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-24 14:00</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1517.5</v>
+        <v>22070</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1558.5</v>
+        <v>22190</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-24 10:30</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.63% (41.0)</t>
+          <t>0.54% (120.0)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1599.5</v>
+        <v>22310</v>
       </c>
       <c r="L15" t="n">
-        <v>1640.5</v>
+        <v>22430</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2761,53 +2451,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2907</v>
+        <v>1650.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:45</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-25 13:15</t>
+          <t>2026-09-28 15:15</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2898.2</v>
+        <v>1637</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-24 14:15</t>
+          <t>2026-09-28 09:30</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2945.7</v>
+        <v>1661.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-24 13:15</t>
+          <t>2026-09-28 09:15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.61% (47.5)</t>
+          <t>1.46% (24.2)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2993.2</v>
+        <v>1685.4</v>
       </c>
       <c r="L16" t="n">
-        <v>3040.7</v>
+        <v>1709.6</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2823,53 +2513,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200.4</v>
+        <v>10983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-09-24 13:30</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-25 10:15</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>196.1</v>
+        <v>10981</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-25 09:45</t>
+          <t>2026-09-28 14:15</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>203.34</v>
+        <v>11042</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-24 11:15</t>
+          <t>2026-09-28 14:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.56% (7.24)</t>
+          <t>0.55% (61.0)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>210.58</v>
+        <v>11103</v>
       </c>
       <c r="L17" t="n">
-        <v>217.82</v>
+        <v>11164</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2877,316 +2567,6 @@
         </is>
       </c>
       <c r="N17" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1219.9</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-25 14:00</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1175.1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-09-24 14:15</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1247.4</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-23 14:15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5.8% (72.3)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1319.7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1392</v>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>10821.29</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:30</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-25 12:15</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>10746</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-25 10:00</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>11023</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:15</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2.51% (277.0)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>11300</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11577</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4933</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-22 12:30</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-25 15:15</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>4883.5</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:45</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>4936</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1.06% (52.5)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>4988.5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>5041</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1242.8</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-24 09:15</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:45</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1202.6</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-09-24 15:00</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>1246</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-09-24 12:15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.48% (43.4)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>1289.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1332.8</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-22 10:30</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-25 13:15</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>161.67</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-09-25 09:15</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>164.85</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1.93% (3.18)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>168.03</v>
-      </c>
-      <c r="L22" t="n">
-        <v>171.21</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,7 +510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -523,35 +523,35 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 12:45</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>195.37</v>
+        <v>192.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>197.36</v>
+        <v>196.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:15</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.01% (1.99)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>199.35</v>
+        <v>200.89</v>
       </c>
       <c r="L2" t="n">
-        <v>201.34</v>
+        <v>205.11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -647,35 +647,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2026-09-28 15:00</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>407.35</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-09-28 12:45</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>416.55</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:15</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.21% (9.2)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>425.75</v>
+        <v>421.05</v>
       </c>
       <c r="L4" t="n">
-        <v>434.95</v>
+        <v>430.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -771,35 +771,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1621</v>
+        <v>1600.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 09:30</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1660.4</v>
+        <v>1642.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.37% (39.4)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1699.8</v>
+        <v>1685.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1739.2</v>
+        <v>1728.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -895,35 +895,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>171.05</v>
+        <v>168.57</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 10:30</t>
+          <t>2026-09-29 10:45</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>172.2</v>
+        <v>173.18</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>2.66% (4.61)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>173.35</v>
+        <v>177.79</v>
       </c>
       <c r="L8" t="n">
-        <v>174.5</v>
+        <v>182.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1081,35 +1081,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-28 11:15</t>
+          <t>2026-09-29 15:15</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>986.6</v>
+        <v>980.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:30</t>
+          <t>2026-09-29 13:30</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>993.4</v>
+        <v>992.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-29 12:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.68% (6.8)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1000.2</v>
+        <v>1005</v>
       </c>
       <c r="L11" t="n">
-        <v>1007</v>
+        <v>1017.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1143,35 +1143,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>396</v>
+        <v>394.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 09:30</t>
+          <t>2026-09-29 09:45</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>402</v>
+        <v>403.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.49% (6.0)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>408</v>
+        <v>412.6</v>
       </c>
       <c r="L12" t="n">
-        <v>414</v>
+        <v>421.55</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1205,35 +1205,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-28 12:15</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11945</v>
+        <v>11832</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 11:45</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12020</v>
+        <v>12000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-28 10:45</t>
+          <t>2026-09-29 09:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.62% (75.0)</t>
+          <t>1.4% (168.0)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12095</v>
+        <v>12168</v>
       </c>
       <c r="L13" t="n">
-        <v>12170</v>
+        <v>12336</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1329,35 +1329,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 14:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22070</v>
+        <v>22025</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22190</v>
+        <v>22195</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.54% (120.0)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22310</v>
+        <v>22365</v>
       </c>
       <c r="L15" t="n">
-        <v>22430</v>
+        <v>22535</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1391,35 +1391,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1665.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1637</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:30</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1661.2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:15</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.46% (24.2)</t>
+          <t>2.1% (35.0)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1685.4</v>
+        <v>1700.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1709.6</v>
+        <v>1735.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1453,35 +1453,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10981</v>
+        <v>10869</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11042</v>
+        <v>11030</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:00</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.55% (61.0)</t>
+          <t>1.46% (161.0)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>11103</v>
+        <v>11191</v>
       </c>
       <c r="L17" t="n">
-        <v>11164</v>
+        <v>11352</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1489,6 +1489,626 @@
         </is>
       </c>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2793.7</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2920.1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4.33% (126.4)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>3046.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3172.9</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:00</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.56% (2.85)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:30</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>272</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1127</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1139.6</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.11% (12.6)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1152.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1247</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:15</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1267.7</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.63% (20.7)</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1309.1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4837</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:30</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>4872</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>4907</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4942</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>4095</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>259</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>260.45</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.65% (4.3)</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>269.05</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1505,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,7 +2208,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1601,35 +2221,35 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 12:45</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>195.37</v>
+        <v>192.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>197.36</v>
+        <v>196.67</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:15</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.01% (1.99)</t>
+          <t>2.15% (4.22)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>199.35</v>
+        <v>200.89</v>
       </c>
       <c r="L2" t="n">
-        <v>201.34</v>
+        <v>205.11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1712,7 +2332,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1725,35 +2345,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>402.75</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>2026-09-28 15:00</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>407.35</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-09-28 12:45</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>416.55</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:15</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.21% (9.2)</t>
+          <t>2.22% (9.15)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>425.75</v>
+        <v>421.05</v>
       </c>
       <c r="L4" t="n">
-        <v>434.95</v>
+        <v>430.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1836,7 +2456,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1849,35 +2469,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 13:15</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1621</v>
+        <v>1600.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 09:30</t>
+          <t>2026-09-29 10:00</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1660.4</v>
+        <v>1642.9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.37% (39.4)</t>
+          <t>2.6% (42.7)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1699.8</v>
+        <v>1685.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1739.2</v>
+        <v>1728.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1960,7 +2580,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1973,35 +2593,35 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>171.05</v>
+        <v>168.57</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 10:30</t>
+          <t>2026-09-29 10:45</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>172.2</v>
+        <v>173.18</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.67% (1.15)</t>
+          <t>2.66% (4.61)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>173.35</v>
+        <v>177.79</v>
       </c>
       <c r="L8" t="n">
-        <v>174.5</v>
+        <v>182.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2146,7 +2766,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2159,35 +2779,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-28 11:15</t>
+          <t>2026-09-29 15:15</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>986.6</v>
+        <v>980.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:30</t>
+          <t>2026-09-29 13:30</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>993.4</v>
+        <v>992.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-28 10:15</t>
+          <t>2026-09-29 12:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.68% (6.8)</t>
+          <t>1.24% (12.3)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1000.2</v>
+        <v>1005</v>
       </c>
       <c r="L11" t="n">
-        <v>1007</v>
+        <v>1017.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2208,7 +2828,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2221,35 +2841,35 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-28 12:00</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>396</v>
+        <v>394.7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 09:30</t>
+          <t>2026-09-29 09:45</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>402</v>
+        <v>403.65</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-28 15:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.49% (6.0)</t>
+          <t>2.22% (8.95)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>408</v>
+        <v>412.6</v>
       </c>
       <c r="L12" t="n">
-        <v>414</v>
+        <v>421.55</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2270,7 +2890,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2283,35 +2903,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-28 12:15</t>
+          <t>2026-09-29 11:45</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11945</v>
+        <v>11832</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 11:45</t>
+          <t>2026-09-29 10:30</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>12020</v>
+        <v>12000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-28 10:45</t>
+          <t>2026-09-29 09:45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.62% (75.0)</t>
+          <t>1.4% (168.0)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12095</v>
+        <v>12168</v>
       </c>
       <c r="L13" t="n">
-        <v>12170</v>
+        <v>12336</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2394,7 +3014,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2407,35 +3027,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 14:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22070</v>
+        <v>22025</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-29 09:30</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>22190</v>
+        <v>22195</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-28 15:00</t>
+          <t>2026-09-29 09:15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.54% (120.0)</t>
+          <t>0.77% (170.0)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>22310</v>
+        <v>22365</v>
       </c>
       <c r="L15" t="n">
-        <v>22430</v>
+        <v>22535</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -2456,7 +3076,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2469,35 +3089,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1630.8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1665.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>2026-09-28 15:15</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1637</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:30</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1661.2</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-09-28 09:15</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.46% (24.2)</t>
+          <t>2.1% (35.0)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1685.4</v>
+        <v>1700.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1709.6</v>
+        <v>1735.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -2518,7 +3138,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2531,35 +3151,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 12:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10981</v>
+        <v>10869</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:15</t>
+          <t>2026-09-29 10:15</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11042</v>
+        <v>11030</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-28 14:00</t>
+          <t>2026-09-28 14:45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.55% (61.0)</t>
+          <t>1.46% (161.0)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>11103</v>
+        <v>11191</v>
       </c>
       <c r="L17" t="n">
-        <v>11164</v>
+        <v>11352</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -2567,6 +3187,626 @@
         </is>
       </c>
       <c r="N17" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2898.2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2793.7</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>2920.1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4.33% (126.4)</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>3046.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3172.9</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1766.7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:45</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:00</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1770.1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.88% (33.3)</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1803.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1836.7</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2391</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:00</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2381.6</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>2420</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.59% (38.4)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2458.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2496.8</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>79.95</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3.56% (2.85)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>263.55</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:00</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>263.3</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:30</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.09% (2.9)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>269.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>272</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1127</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:30</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1139.6</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.11% (12.6)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1152.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1164.8</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1264.4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:30</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:15</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1247</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-29 10:15</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1267.7</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.63% (20.7)</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1288.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1309.1</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4848.5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:45</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>4837</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-09-29 13:30</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>4872</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-29 12:30</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.72% (35.0)</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>4907</v>
+      </c>
+      <c r="L25" t="n">
+        <v>4942</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4057</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4043.3</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:15</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>4095</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.26% (51.7)</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>4146.7</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4198.4</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>259</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-29 15:00</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>256.15</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:00</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>260.45</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-29 11:30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.65% (4.3)</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>269.05</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-09-30 14:30</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 12:45</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 14:30</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:45</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -3418,6 +3418,68 @@
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1091.9</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>3.43% (38.8)</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>1169.5</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>1208.3</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -3434,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3670,7 +3732,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 10:45</t>
+          <t>2026-09-30 14:30</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -3918,7 +3980,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 10:30</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -4228,7 +4290,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -4352,7 +4414,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -4414,7 +4476,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 13:45</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -4538,7 +4600,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -4662,7 +4724,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 10:00</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -4848,7 +4910,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -4910,7 +4972,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -5096,7 +5158,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 12:45</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
@@ -5220,7 +5282,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:15</t>
+          <t>2026-09-30 14:30</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -5282,7 +5344,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-09-30 15:15</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -5468,7 +5530,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
@@ -5530,7 +5592,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -5592,7 +5654,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:45</t>
+          <t>2026-09-30 14:15</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -6026,7 +6088,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -6150,7 +6212,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 12:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -6310,6 +6372,68 @@
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-28 12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1091.9</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30 10:30</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>1130.7</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:45</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>3.43% (38.8)</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>1169.5</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>1208.3</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 10:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1522,35 +1522,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:15</t>
+          <t>2026-10-01 14:00</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1665.8</v>
+        <v>1651.1</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-10-01 12:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.1% (35.0)</t>
+          <t>2.0% (33.0)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1700.8</v>
+        <v>1684.1</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1735.8</v>
+        <v>1717.1</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -1770,35 +1770,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2026-10-01 15:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2377</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:30</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>2026-09-30 15:15</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>2381.6</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>2420</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:15</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.07% (25.6)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2458.4</v>
+        <v>2428.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2496.8</v>
+        <v>2453.8</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 11:15</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -2948,35 +2948,35 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>442.8</v>
+        <v>441.8</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-10-01 14:00</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>447.8</v>
+        <v>448.55</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30 10:15</t>
+          <t>2026-10-01 13:00</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>1.12% (5.0)</t>
+          <t>1.5% (6.75)</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>452.8</v>
+        <v>455.3</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>457.8</v>
+        <v>462.05</v>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -3072,35 +3072,35 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-10-01 13:00</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>448.55</v>
+        <v>447.25</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>458.65</v>
+        <v>459.65</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2.2% (10.1)</t>
+          <t>2.7% (12.4)</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>468.75</v>
+        <v>472.05</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>478.85</v>
+        <v>484.45</v>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -3196,35 +3196,35 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>159.41</v>
+        <v>158.51</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>162.37</v>
+        <v>163.52</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>3.06% (5.01)</t>
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>165.33</v>
+        <v>168.53</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>168.29</v>
+        <v>173.54</v>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -3480,6 +3480,192 @@
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:00</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>878.6</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2.78% (24.4)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>903</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>927.4</v>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>1677.7</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>1704</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:00</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>1.54% (26.3)</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>1730.3</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>1756.6</v>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>422</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:30</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>425.85</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:00</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (10.1)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>435.95</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -3496,7 +3682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3608,7 +3794,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29 12:45</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -3732,7 +3918,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -3980,7 +4166,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 10:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
@@ -4463,7 +4649,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -4476,35 +4662,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 13:45</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1630.8</v>
+        <v>1618.1</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:15</t>
+          <t>2026-10-01 14:00</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1665.8</v>
+        <v>1651.1</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-10-01 12:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.1% (35.0)</t>
+          <t>2.0% (33.0)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>1700.8</v>
+        <v>1684.1</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1735.8</v>
+        <v>1717.1</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -4662,7 +4848,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29 14:45</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -4711,7 +4897,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -4724,35 +4910,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2026-10-01 15:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2377</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:30</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>2402.6</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>2026-09-30 15:15</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>2381.6</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-29 09:30</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>2420</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-28 15:15</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.59% (38.4)</t>
+          <t>1.07% (25.6)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>2458.4</v>
+        <v>2428.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2496.8</v>
+        <v>2453.8</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -5220,7 +5406,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
@@ -5282,7 +5468,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 14:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
@@ -5406,7 +5592,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 11:15</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
@@ -5592,7 +5778,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 14:45</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -5716,7 +5902,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F36" s="6" t="n">
@@ -5840,7 +6026,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 09:30</t>
+          <t>2026-10-01 14:45</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
@@ -5889,7 +6075,7 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -5902,35 +6088,35 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 12:30</t>
+          <t>2026-10-01 14:15</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
-        <v>442.8</v>
+        <v>441.8</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>2026-09-30 12:00</t>
+          <t>2026-10-01 14:00</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>447.8</v>
+        <v>448.55</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30 10:15</t>
+          <t>2026-10-01 13:00</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>1.12% (5.0)</t>
+          <t>1.5% (6.75)</t>
         </is>
       </c>
       <c r="K39" s="13" t="n">
-        <v>452.8</v>
+        <v>455.3</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>457.8</v>
+        <v>462.05</v>
       </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
@@ -6013,7 +6199,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -6026,35 +6212,35 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 11:30</t>
+          <t>2026-10-01 13:00</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>448.55</v>
+        <v>447.25</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>458.65</v>
+        <v>459.65</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 09:15</t>
+          <t>2026-09-30 14:45</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>2.2% (10.1)</t>
+          <t>2.7% (12.4)</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>468.75</v>
+        <v>472.05</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>478.85</v>
+        <v>484.45</v>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -6088,7 +6274,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30 15:00</t>
+          <t>2026-10-01 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -6137,7 +6323,7 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -6150,35 +6336,35 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>2026-09-29 11:00</t>
+          <t>2026-10-01 11:30</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
-        <v>159.41</v>
+        <v>158.51</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>2026-09-29 09:30</t>
+          <t>2026-10-01 09:15</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>162.37</v>
+        <v>163.52</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28 15:15</t>
+          <t>2026-09-30 15:00</t>
         </is>
       </c>
       <c r="J43" s="11" t="inlineStr">
         <is>
-          <t>1.82% (2.96)</t>
+          <t>3.06% (5.01)</t>
         </is>
       </c>
       <c r="K43" s="13" t="n">
-        <v>165.33</v>
+        <v>168.53</v>
       </c>
       <c r="L43" s="13" t="n">
-        <v>168.29</v>
+        <v>173.54</v>
       </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
@@ -6274,7 +6460,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>2026-09-30 09:15</t>
+          <t>2026-10-01 14:30</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -6434,6 +6620,192 @@
         </is>
       </c>
       <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28 09:15</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 15:00</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:15</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>878.6</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-28 10:00</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2.78% (24.4)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>903</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>927.4</v>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>1699.9</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-30 11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>1677.7</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:15</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>1704</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:00</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>1.54% (26.3)</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>1730.3</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>1756.6</v>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>422</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:30</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:00</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>425.85</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:00</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2.37% (10.1)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>435.95</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,53 +636,53 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>378.65</v>
+        <v>7910</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-06 09:15</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-06 15:15</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>377.05</v>
+        <v>7807.5</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-06 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>384.35</v>
+        <v>8005</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 14:45</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>2.47% (197.5)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>391.65</v>
+        <v>8202.5</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>398.95</v>
+        <v>8400</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -707,44 +707,44 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>296.5</v>
+        <v>378.65</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 11:15</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 15:00</t>
+          <t>2026-10-05 12:15</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>294.55</v>
+        <v>377.05</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 12:30</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>296.8</v>
+        <v>384.35</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 11:30</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>0.76% (2.25)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>299.05</v>
+        <v>391.65</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>301.3</v>
+        <v>398.95</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -769,44 +769,44 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4737</v>
+        <v>296.5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 11:15</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-06 14:45</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4734.1</v>
+        <v>294.55</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 12:30</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>4770.2</v>
+        <v>296.8</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:45</t>
+          <t>2026-10-05 11:30</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>0.76% (2.25)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4806.3</v>
+        <v>299.05</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4842.4</v>
+        <v>301.3</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
@@ -831,44 +831,44 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1333.4</v>
+        <v>4737</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:45</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1321.3</v>
+        <v>4734.1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 10:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1334</v>
+        <v>4770.2</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 13:45</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0.95% (12.7)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>1346.7</v>
+        <v>4806.3</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>1359.4</v>
+        <v>4842.4</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1194.9</v>
+        <v>1333.4</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -902,35 +902,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>2026-10-06 11:15</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1321.3</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1334</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>1189.9</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-05 09:15</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>1202.9</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 09:15</t>
-        </is>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.95% (12.7)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1215.9</v>
+        <v>1346.7</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1228.9</v>
+        <v>1359.4</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>5051</v>
+        <v>1194.9</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -964,19 +964,19 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:45</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4995.5</v>
+        <v>1189.9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>5200</v>
+        <v>1202.9</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -985,14 +985,14 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>3.93% (204.5)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>5404.5</v>
+        <v>1215.9</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>5609</v>
+        <v>1228.9</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1017,44 +1017,44 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1295</v>
+        <v>5051</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:15</t>
+          <t>2026-10-06 09:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1293</v>
+        <v>4995.5</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1299.4</v>
+        <v>5200</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:45</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>3.93% (204.5)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1305.8</v>
+        <v>5404.5</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1312.2</v>
+        <v>5609</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1079,44 +1079,44 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>4717.3</v>
+        <v>1295</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 10:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 11:45</t>
+          <t>2026-10-06 12:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4710</v>
+        <v>1293</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 11:00</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>4724.4</v>
+        <v>1299.4</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 10:45</t>
+          <t>2026-10-05 13:45</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.3% (14.4)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4738.8</v>
+        <v>1305.8</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>4753.2</v>
+        <v>1312.2</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1132,60 +1132,804 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:30</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1505.4</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:00</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1539.5</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2.22% (34.1)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1573.6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1607.7</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>4702.5</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>4777.2</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>1.56% (74.7)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>4851.9</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>4926.6</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>3930.1</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>3920</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H12" s="8" t="n">
         <v>4031.6</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2.77% (111.6)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>4143.2</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>4254.8</v>
       </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:00</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:30</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2336.9</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:00</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2393.6</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:45</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>2.37% (56.7)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>2450.3</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>2507</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:15</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (2.51)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>2944.4</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:45</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:30</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2936.1</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2955</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:45</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0.64% (18.9)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>2973.9</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>2992.8</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:45</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>701</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>706.6</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:45</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>0.79% (5.6)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>712.2</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:45</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>1.06% (1.39)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>76.51000000000001</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>76.06999999999999</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:00</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:30</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>1.36% (1.05)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1079</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1097.3</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:00</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>5.6% (61.5)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1158.8</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1220.3</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>918.6</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:30</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2.8% (25.7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>944.3</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>3709.5</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3695</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>3723.8</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.77% (28.8)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>3752.6</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>3781.4</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1792.6</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1769.1</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1797.1</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:30</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>1.56% (28.0)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1825.1</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1853.1</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1202,7 +1946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1296,53 +2040,53 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>378.65</v>
+        <v>7910</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-06 09:15</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-06 15:15</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>377.05</v>
+        <v>7807.5</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-06 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>384.35</v>
+        <v>8005</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 14:45</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>1.9% (7.3)</t>
+          <t>2.47% (197.5)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>391.65</v>
+        <v>8202.5</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>398.95</v>
+        <v>8400</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -1358,7 +2102,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1367,44 +2111,44 @@
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>296.5</v>
+        <v>378.65</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 11:15</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 15:00</t>
+          <t>2026-10-05 12:15</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>294.55</v>
+        <v>377.05</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 12:30</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>296.8</v>
+        <v>384.35</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 11:30</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>0.76% (2.25)</t>
+          <t>1.9% (7.3)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>299.05</v>
+        <v>391.65</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>301.3</v>
+        <v>398.95</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -1420,7 +2164,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1429,44 +2173,44 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4737</v>
+        <v>296.5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 11:15</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-06 14:45</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>4734.1</v>
+        <v>294.55</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 12:30</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>4770.2</v>
+        <v>296.8</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:45</t>
+          <t>2026-10-05 11:30</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>0.76% (36.1)</t>
+          <t>0.76% (2.25)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4806.3</v>
+        <v>299.05</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4842.4</v>
+        <v>301.3</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -1482,7 +2226,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
@@ -1491,44 +2235,44 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>1333.4</v>
+        <v>4737</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:45</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1321.3</v>
+        <v>4734.1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 10:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1334</v>
+        <v>4770.2</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-05 13:45</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0.95% (12.7)</t>
+          <t>0.76% (36.1)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>1346.7</v>
+        <v>4806.3</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>1359.4</v>
+        <v>4842.4</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -1544,7 +2288,7 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1553,7 +2297,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1194.9</v>
+        <v>1333.4</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -1562,35 +2306,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>2026-10-06 11:15</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1321.3</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1334</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
-        <v>1189.9</v>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-05 09:15</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>1202.9</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 09:15</t>
-        </is>
-      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.95% (12.7)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1215.9</v>
+        <v>1346.7</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1228.9</v>
+        <v>1359.4</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1606,7 +2350,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -1615,7 +2359,7 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>5051</v>
+        <v>1194.9</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -1624,19 +2368,19 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:45</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4995.5</v>
+        <v>1189.9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:30</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>5200</v>
+        <v>1202.9</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1645,14 +2389,14 @@
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>3.93% (204.5)</t>
+          <t>1.08% (13.0)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>5404.5</v>
+        <v>1215.9</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>5609</v>
+        <v>1228.9</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1668,7 +2412,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1677,44 +2421,44 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1295</v>
+        <v>5051</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:15</t>
+          <t>2026-10-06 09:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1293</v>
+        <v>4995.5</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:00</t>
+          <t>2026-10-05 09:30</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1299.4</v>
+        <v>5200</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:45</t>
+          <t>2026-10-05 09:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>0.49% (6.4)</t>
+          <t>3.93% (204.5)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1305.8</v>
+        <v>5404.5</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1312.2</v>
+        <v>5609</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1730,7 +2474,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
@@ -1739,44 +2483,44 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>4717.3</v>
+        <v>1295</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 10:15</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 11:45</t>
+          <t>2026-10-06 12:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4710</v>
+        <v>1293</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 11:00</t>
+          <t>2026-10-05 14:00</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>4724.4</v>
+        <v>1299.4</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 10:45</t>
+          <t>2026-10-05 13:45</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.3% (14.4)</t>
+          <t>0.49% (6.4)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>4738.8</v>
+        <v>1305.8</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>4753.2</v>
+        <v>1312.2</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1792,60 +2536,804 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:30</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1505.4</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 10:00</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1539.5</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2.22% (34.1)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1573.6</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1607.7</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>4717.3</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:15</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>4702.5</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>4777.2</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>1.56% (74.7)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>4851.9</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>4926.6</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>TVSMOTOR</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>3930.1</v>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>3920</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H12" s="8" t="n">
         <v>4031.6</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>2026-10-05 09:15</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>2.77% (111.6)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>4143.2</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>4254.8</v>
       </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>2377</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 10:00</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:30</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2336.9</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:00</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2393.6</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:45</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>2.37% (56.7)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>2450.3</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>2507</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:30</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:15</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:00</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (2.51)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>174.01</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>2944.4</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:45</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:30</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2936.1</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:00</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2955</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:45</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0.64% (18.9)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>2973.9</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>2992.8</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>706.25</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:45</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>701</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>706.6</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:45</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>0.79% (5.6)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>712.2</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>717.8</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>129.72</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>131.11</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:45</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>1.06% (1.39)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>76.51000000000001</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 12:00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>76.06999999999999</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:00</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:30</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>1.36% (1.05)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1079</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:45</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1097.3</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 15:00</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>5.6% (61.5)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1158.8</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1220.3</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>902.05</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>892.9</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>918.6</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:30</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2.8% (25.7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>944.3</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>970</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>3709.5</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:00</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3695</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>3723.8</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.77% (28.8)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>3752.6</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>3781.4</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1792.6</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:15</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:00</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1769.1</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:15</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1797.1</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:30</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>1.56% (28.0)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1825.1</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1853.1</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-07 14:45</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 14:45</t>
+          <t>2026-10-07 13:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -902,7 +902,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -976,23 +976,23 @@
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1202.9</v>
+        <v>1198.7</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.73% (8.8)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1215.9</v>
+        <v>1207.5</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1228.9</v>
+        <v>1216.3</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1150,15 +1150,15 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:30</t>
+          <t>2026-10-07 10:45</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1505.4</v>
+        <v>1493.6</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:00</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
@@ -1171,14 +1171,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.22% (34.1)</t>
+          <t>2.98% (45.9)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1573.6</v>
+        <v>1585.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1607.7</v>
+        <v>1631.3</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3920</v>
+        <v>3870.8</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 10:30</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>4031.6</v>
+        <v>3977</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 10:15</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>2.67% (106.2)</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4143.2</v>
+        <v>4083.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4254.8</v>
+        <v>4189.4</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 11:30</t>
+          <t>2026-10-07 10:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -1460,35 +1460,35 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 12:30</t>
+          <t>2026-10-07 11:30</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2936.1</v>
+        <v>2928.9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 12:00</t>
+          <t>2026-10-07 10:00</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>2955</v>
+        <v>2969</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06 11:45</t>
+          <t>2026-10-06 15:15</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0.64% (18.9)</t>
+          <t>1.35% (40.1)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>2973.9</v>
+        <v>3009.1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>2992.8</v>
+        <v>3049.2</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45</t>
+          <t>2026-10-07 10:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1646,35 +1646,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76.06999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 15:00</t>
+          <t>2026-10-07 13:00</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>77.12</v>
+        <v>76.97</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.36% (1.05)</t>
+          <t>1.18% (0.91)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>78.17</v>
+        <v>77.88</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>79.22</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -1770,35 +1770,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2026-10-07 13:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:30</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>903</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>2026-10-06 15:00</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>892.9</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:30</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.8% (25.7)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>944.3</v>
+        <v>914.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>970</v>
+        <v>925.4</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1930,6 +1930,254 @@
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:15</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>1.75% (6.3)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>949.9</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:30</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>0.44% (4.2)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>954.1</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>958.3</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>936</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:15</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>930</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>960</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:00</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>3.12% (30.0)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>990</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:30</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>10595</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>10759</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (164.0)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>10923</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>11087</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1946,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2058,7 +2306,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:15</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
@@ -2120,7 +2368,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 12:15</t>
+          <t>2026-10-07 14:45</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -2182,7 +2430,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 14:45</t>
+          <t>2026-10-07 13:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -2306,7 +2554,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 11:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -2368,7 +2616,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -2380,23 +2628,23 @@
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1202.9</v>
+        <v>1198.7</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.08% (13.0)</t>
+          <t>0.73% (8.8)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1215.9</v>
+        <v>1207.5</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1228.9</v>
+        <v>1216.3</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -2541,7 +2789,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -2554,15 +2802,15 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 10:30</t>
+          <t>2026-10-07 10:45</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1505.4</v>
+        <v>1493.6</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 10:00</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
@@ -2575,14 +2823,14 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.22% (34.1)</t>
+          <t>2.98% (45.9)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1573.6</v>
+        <v>1585.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1607.7</v>
+        <v>1631.3</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -2616,7 +2864,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -2665,7 +2913,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2678,35 +2926,35 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3920</v>
+        <v>3870.8</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 10:30</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>4031.6</v>
+        <v>3977</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-07 10:15</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.77% (111.6)</t>
+          <t>2.67% (106.2)</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4143.2</v>
+        <v>4083.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4254.8</v>
+        <v>4189.4</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -2740,7 +2988,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 11:30</t>
+          <t>2026-10-07 10:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -2851,7 +3099,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -2864,35 +3112,35 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-06 12:30</t>
+          <t>2026-10-07 11:30</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>2936.1</v>
+        <v>2928.9</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 12:00</t>
+          <t>2026-10-07 10:00</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>2955</v>
+        <v>2969</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06 11:45</t>
+          <t>2026-10-06 15:15</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0.64% (18.9)</t>
+          <t>1.35% (40.1)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>2973.9</v>
+        <v>3009.1</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>2992.8</v>
+        <v>3049.2</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -2926,7 +3174,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:45</t>
+          <t>2026-10-07 10:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -3037,7 +3285,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3050,35 +3298,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
+          <t>2026-10-07 14:15</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76.06999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 15:00</t>
+          <t>2026-10-07 13:00</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>77.12</v>
+        <v>76.97</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:30</t>
+          <t>2026-10-07 12:00</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.36% (1.05)</t>
+          <t>1.18% (0.91)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>78.17</v>
+        <v>77.88</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>79.22</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -3161,7 +3409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -3174,35 +3422,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
+          <t>2026-10-07 13:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>891.8</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 09:30</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>903</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
           <t>2026-10-06 15:00</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n">
-        <v>892.9</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>918.6</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:30</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.8% (25.7)</t>
+          <t>1.24% (11.2)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>944.3</v>
+        <v>914.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>970</v>
+        <v>925.4</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -3298,7 +3546,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 15:00</t>
+          <t>2026-10-07 09:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -3334,6 +3582,254 @@
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>AMBUJACEM</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>352.8</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:15</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>1.75% (6.3)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>365.4</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>945.8</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>945.7</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:00</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>949.9</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:30</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>0.44% (4.2)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>954.1</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>958.3</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>936</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:15</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>930</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>960</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:00</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>3.12% (30.0)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>990</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>10612</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:30</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>10595</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>10759</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:00</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (164.0)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>10923</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>11087</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -964,35 +964,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1189.9</v>
+        <v>1189.5</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-08 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1198.7</v>
+        <v>1203.8</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-07 15:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0.73% (8.8)</t>
+          <t>1.19% (14.3)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1207.5</v>
+        <v>1218.1</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1216.3</v>
+        <v>1232.4</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1150,35 +1150,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>2026-10-08 11:30</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1487</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1513</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
           <t>2026-10-07 10:45</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>1493.6</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>1539.5</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.98% (45.9)</t>
+          <t>1.72% (26.0)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1585.4</v>
+        <v>1539</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1631.3</v>
+        <v>1565</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 11:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-08 10:30</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07 14:15</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2178,6 +2178,316 @@
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1209.4</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1282</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:45</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>5.66% (72.6)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>1354.6</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>1427.2</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1702.1</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1701</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>0.53% (9.1)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>1719.2</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>253.2</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>0.86% (2.2)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1658.6</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1684.2</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (25.6)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1709.8</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1735.4</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1308.7</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>1.13% (15.0)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>1338.7</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2194,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2603,7 +2913,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -2616,35 +2926,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1189.9</v>
+        <v>1189.5</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:15</t>
+          <t>2026-10-08 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1198.7</v>
+        <v>1203.8</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-07 15:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0.73% (8.8)</t>
+          <t>1.19% (14.3)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1207.5</v>
+        <v>1218.1</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1216.3</v>
+        <v>1232.4</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -2802,35 +3112,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>2026-10-08 11:30</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1487</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1513</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
           <t>2026-10-07 10:45</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>1493.6</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-07 09:15</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>1539.5</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.98% (45.9)</t>
+          <t>1.72% (26.0)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>1585.4</v>
+        <v>1539</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1631.3</v>
+        <v>1565</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -2926,7 +3236,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:30</t>
+          <t>2026-10-08 11:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -3050,7 +3360,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06 09:30</t>
+          <t>2026-10-08 10:30</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
@@ -3732,7 +4042,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07 14:15</t>
+          <t>2026-10-08 10:00</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -3830,6 +4140,316 @@
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1223.6</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:00</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1209.4</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1282</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:45</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>5.66% (72.6)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>1354.6</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>1427.2</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1702.1</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1701</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1710.1</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>0.53% (9.1)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>1719.2</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>1728.3</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>254.65</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>253.2</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>0.86% (2.2)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>259.8</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1674.8</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1658.6</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:30</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1684.2</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (25.6)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1709.8</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1735.4</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>1316.5</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:15</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>1308.7</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>1.13% (15.0)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>1338.7</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>1353.7</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
@@ -654,35 +654,35 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>2026-10-09 12:30</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>7608</v>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>7917</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
           <t>2026-10-07 15:00</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>7807.5</v>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>8005</v>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:45</t>
-        </is>
-      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2.47% (197.5)</t>
+          <t>3.9% (309.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>8202.5</v>
+        <v>8226</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>8400</v>
+        <v>8535</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -964,35 +964,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 13:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1189.5</v>
+        <v>1167.4</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08 09:15</t>
+          <t>2026-10-08 12:45</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1203.8</v>
+        <v>1201</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15</t>
+          <t>2026-10-08 09:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.19% (14.3)</t>
+          <t>2.8% (33.6)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1218.1</v>
+        <v>1234.6</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1232.4</v>
+        <v>1268.2</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 11:30</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1522,35 +1522,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:30</t>
+          <t>2026-10-09 13:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>701</v>
+        <v>690.55</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
+          <t>2026-10-08 13:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>706.6</v>
+        <v>706.9</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:45</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>0.79% (5.6)</t>
+          <t>2.31% (16.35)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>712.2</v>
+        <v>723.25</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>717.8</v>
+        <v>739.6</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>945.7</v>
+        <v>937.55</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00</t>
+          <t>2026-10-08 14:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>949.9</v>
+        <v>951.3</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:30</t>
+          <t>2026-10-08 10:30</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.44% (4.2)</t>
+          <t>1.45% (13.75)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>954.1</v>
+        <v>965.05</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>958.3</v>
+        <v>978.8</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
@@ -2080,35 +2080,35 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>930</v>
+        <v>917.25</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:00</t>
+          <t>2026-10-08 15:15</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>960</v>
+        <v>938.7</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:00</t>
+          <t>2026-10-08 11:15</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>3.12% (30.0)</t>
+          <t>2.29% (21.45)</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>990</v>
+        <v>960.15</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>1020</v>
+        <v>981.6</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -2142,35 +2142,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:30</t>
+          <t>2026-10-09 13:15</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10595</v>
+        <v>10426</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:00</t>
+          <t>2026-10-08 15:00</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>10759</v>
+        <v>10690</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 12:00</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (164.0)</t>
+          <t>2.47% (264.0)</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>10923</v>
+        <v>10954</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>11087</v>
+        <v>11218</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -2488,6 +2488,626 @@
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>6660.5</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>6578</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>6789</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>3.11% (211.0)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>7211</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:45</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1750.1</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>4.29% (75.1)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1900.3</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:45</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>864.45</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2.81% (24.3)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>888.75</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>913.05</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1567.7</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>1.57% (24.6)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1592.3</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1616.9</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:15</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>4671.1</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>4792.4</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2.53% (121.3)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>4913.7</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>5035</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>6840</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>6767.5</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>6872</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>1.52% (104.5)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>6976.5</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>7081</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>3655.9</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>3607.1</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:45</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>3673.5</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>1.81% (66.4)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>3739.9</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3806.3</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>3936</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>3908.4</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>3941.6</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:15</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>0.84% (33.2)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>3974.8</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>4008</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>11305</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>11225</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11342</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:45</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>1.03% (117.0)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>11459</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>11576</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:45</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:00</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:45</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>220.85</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:45</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (2.1)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>225.05</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2504,7 +3124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2603,7 +3223,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
@@ -2616,35 +3236,35 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>2026-10-09 12:30</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>7608</v>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:15</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>7917</v>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
           <t>2026-10-07 15:00</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>7807.5</v>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06 09:15</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>8005</v>
-      </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:45</t>
-        </is>
-      </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2.47% (197.5)</t>
+          <t>3.9% (309.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>8202.5</v>
+        <v>8226</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>8400</v>
+        <v>8535</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -2926,35 +3546,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 13:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1189.5</v>
+        <v>1167.4</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08 09:15</t>
+          <t>2026-10-08 12:45</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1203.8</v>
+        <v>1201</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 15:15</t>
+          <t>2026-10-08 09:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.19% (14.3)</t>
+          <t>2.8% (33.6)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>1218.1</v>
+        <v>1234.6</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>1232.4</v>
+        <v>1268.2</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -3112,7 +3732,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08 11:30</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -3471,7 +4091,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -3484,35 +4104,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 10:30</t>
+          <t>2026-10-09 13:30</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>701</v>
+        <v>690.55</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06 09:15</t>
+          <t>2026-10-08 13:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>706.6</v>
+        <v>706.9</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:45</t>
+          <t>2026-10-07 14:30</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>0.79% (5.6)</t>
+          <t>2.31% (16.35)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>712.2</v>
+        <v>723.25</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>717.8</v>
+        <v>739.6</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -3967,7 +4587,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -3980,35 +4600,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00</t>
+          <t>2026-10-09 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>945.7</v>
+        <v>937.55</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 14:00</t>
+          <t>2026-10-08 14:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>949.9</v>
+        <v>951.3</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 13:30</t>
+          <t>2026-10-08 10:30</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.44% (4.2)</t>
+          <t>1.45% (13.75)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>954.1</v>
+        <v>965.05</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>958.3</v>
+        <v>978.8</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -4029,7 +4649,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
@@ -4042,35 +4662,35 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-08 10:00</t>
+          <t>2026-10-09 12:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>930</v>
+        <v>917.25</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:00</t>
+          <t>2026-10-08 15:15</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>960</v>
+        <v>938.7</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 10:00</t>
+          <t>2026-10-08 11:15</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>3.12% (30.0)</t>
+          <t>2.29% (21.45)</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>990</v>
+        <v>960.15</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>1020</v>
+        <v>981.6</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -4091,7 +4711,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
@@ -4104,35 +4724,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07 13:30</t>
+          <t>2026-10-09 13:15</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>10595</v>
+        <v>10426</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07 13:00</t>
+          <t>2026-10-08 15:00</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>10759</v>
+        <v>10690</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07 12:00</t>
+          <t>2026-10-07 15:00</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (164.0)</t>
+          <t>2.47% (264.0)</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>10923</v>
+        <v>10954</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>11087</v>
+        <v>11218</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -4450,6 +5070,626 @@
         </is>
       </c>
       <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>6660.5</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>6578</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>6789</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>3.11% (211.0)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>7211</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>1716</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:45</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1750.1</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>4.29% (75.1)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>1825.2</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1900.3</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>854.2</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:45</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>864.45</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2.81% (24.3)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>888.75</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>913.05</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>1563.2</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1543.1</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1567.7</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>1.57% (24.6)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1592.3</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1616.9</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:15</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>4671.1</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>4792.4</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2.53% (121.3)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>4913.7</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>5035</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>6840</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:00</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:15</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>6767.5</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 15:00</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>6872</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 13:30</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>1.52% (104.5)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>6976.5</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>7081</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>3655.9</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>3607.1</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:45</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>3673.5</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>1.81% (66.4)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>3739.9</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>3806.3</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>3936</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-07 13:00</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:30</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>3908.4</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07 15:00</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>3941.6</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:15</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>0.84% (33.2)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>3974.8</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>4008</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>11305</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:30</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>11225</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>11342</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 11:45</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>1.03% (117.0)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>11459</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>11576</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>220.6</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-08 09:45</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:00</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-08 12:45</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>220.85</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-08 10:45</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (2.1)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>225.05</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,10 +542,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -554,7 +554,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 14:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -884,53 +884,53 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>308.45</v>
+        <v>4782.2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 10:30</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 14:15</t>
+          <t>2026-10-13 14:30</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>305.85</v>
+        <v>4749.6</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00</t>
+          <t>2026-10-13 11:15</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>314.3</v>
+        <v>4815.5</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 09:30</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.69% (8.45)</t>
+          <t>1.37% (65.9)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>322.75</v>
+        <v>4881.4</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>331.2</v>
+        <v>4947.3</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -955,44 +955,44 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>441.05</v>
+        <v>308.45</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-12 10:30</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 12:30</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>441</v>
+        <v>305.85</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-12 12:00</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>445.8</v>
+        <v>314.3</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 14:30</t>
+          <t>2026-10-12 09:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.08% (4.8)</t>
+          <t>2.69% (8.45)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>450.6</v>
+        <v>322.75</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>455.4</v>
+        <v>331.2</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1008,60 +1008,804 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>440.55</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>445.8</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>1.18% (5.25)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>451.05</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>456.3</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C9" s="13" t="n">
         <v>1658.1</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>1658</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H9" s="8" t="n">
         <v>1673.9</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>2026-10-12 12:45</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>0.95% (15.9)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K9" s="13" t="n">
         <v>1689.8</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L9" s="13" t="n">
         <v>1705.7</v>
       </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:00</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2.23% (4.18)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>835</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>867.5</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>3.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>932.5</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>166.83</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:00</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (0.96)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>895.4</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:15</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>1.44% (12.9)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>908.3</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>921.2</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:45</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1818.5</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1829.2</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:45</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (10.7)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1839.9</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1850.6</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>857</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>846.1</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>861.85</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:30</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>1.83% (15.75)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>877.6</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>893.35</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:15</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>1.79% (2.28)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>129.56</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>3607</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>3627.5</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (34.3)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>3661.8</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>3696.1</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11225</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:45</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>11130</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:30</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>11325</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>1.72% (195.0)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>11520</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>11715</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1160.2</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:15</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1152.6</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1166.7</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1.21% (14.1)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1180.8</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1443.3</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1508</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>4.29% (64.7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1078,10 +1822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -1090,7 +1834,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
@@ -1252,7 +1996,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 14:45</t>
+          <t>2026-10-13 09:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -1314,7 +2058,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -1420,53 +2164,53 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>308.45</v>
+        <v>4782.2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 10:30</t>
+          <t>2026-10-13 09:15</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12 14:15</t>
+          <t>2026-10-13 14:30</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>305.85</v>
+        <v>4749.6</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 12:00</t>
+          <t>2026-10-13 11:15</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>314.3</v>
+        <v>4815.5</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 09:30</t>
+          <t>2026-10-13 09:45</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.69% (8.45)</t>
+          <t>1.37% (65.9)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>322.75</v>
+        <v>4881.4</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>331.2</v>
+        <v>4947.3</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1482,7 +2226,7 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -1491,44 +2235,44 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>441.05</v>
+        <v>308.45</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-12 10:30</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-13 12:30</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>441</v>
+        <v>305.85</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-12 12:00</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>445.8</v>
+        <v>314.3</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 14:30</t>
+          <t>2026-10-12 09:30</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>1.08% (4.8)</t>
+          <t>2.69% (8.45)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>450.6</v>
+        <v>322.75</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>455.4</v>
+        <v>331.2</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1544,60 +2288,804 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>440.55</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>445.8</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>1.18% (5.25)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>451.05</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>456.3</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
           <t>SBILIFE</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C9" s="13" t="n">
         <v>1658.1</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>1658</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>2026-10-12 13:45</t>
         </is>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H9" s="8" t="n">
         <v>1673.9</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>2026-10-12 12:45</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J9" s="11" t="inlineStr">
         <is>
           <t>0.95% (15.9)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="K9" s="13" t="n">
         <v>1689.8</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L9" s="13" t="n">
         <v>1705.7</v>
       </c>
-      <c r="M8" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:00</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>182.87</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>187.05</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2.23% (4.18)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>195.41</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>840.15</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>835</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>867.5</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>3.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>932.5</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>166.3</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:45</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>166.83</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:00</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (0.96)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>167.79</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>886.5</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:45</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>882.5</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>895.4</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 12:15</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>1.44% (12.9)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>908.3</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>921.2</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:45</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1818.5</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:00</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1829.2</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:45</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>0.58% (10.7)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1839.9</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1850.6</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>857</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>846.1</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:30</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>861.85</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:30</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>1.83% (15.75)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>877.6</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>893.35</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>125.27</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:30</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:15</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>1.79% (2.28)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>129.56</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>131.84</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>3607</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>3593.2</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>3627.5</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:15</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (34.3)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>3661.8</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>3696.1</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11225</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:45</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>11130</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:30</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>11325</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:30</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>1.72% (195.0)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>11520</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>11715</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1160.2</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-12 11:15</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 14:15</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1152.6</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:45</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1166.7</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 10:00</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1.21% (14.1)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>1180.8</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>1194.9</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1486.2</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1443.3</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12 09:15</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1508</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>4.29% (64.7)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1572.7</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1637.4</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -1088,35 +1088,35 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 13:45</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 13:45</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1673.9</v>
+        <v>1666.2</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 12:45</t>
+          <t>2026-10-14 11:30</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.61% (10.2)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1689.8</v>
+        <v>1676.4</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1705.7</v>
+        <v>1686.6</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 11:45</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1806,6 +1806,130 @@
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>461</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:30</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:00</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>461.75</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.92% (4.25)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>466</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1770.7</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:15</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>1.55% (27.5)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1798.2</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1825.7</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1822,7 +1946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2182,7 +2306,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -2355,7 +2479,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -2368,35 +2492,35 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12 13:45</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12 13:45</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1673.9</v>
+        <v>1666.2</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 12:45</t>
+          <t>2026-10-14 11:30</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.95% (15.9)</t>
+          <t>0.61% (10.2)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1689.8</v>
+        <v>1676.4</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1705.7</v>
+        <v>1686.6</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -2554,7 +2678,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 11:45</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -2616,7 +2740,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -2802,7 +2926,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-14 09:15</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -2864,7 +2988,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
+          <t>2026-10-14 13:15</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -3086,6 +3210,130 @@
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>461</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 11:30</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:00</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>461.75</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 12:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.92% (4.25)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>466</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>470.25</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1743.2</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:30</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1770.7</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:15</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>1.55% (27.5)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1798.2</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1825.7</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -902,35 +902,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4749.6</v>
+        <v>4679.7</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13 11:15</t>
+          <t>2026-10-14 13:30</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>4815.5</v>
+        <v>4827.8</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.37% (65.9)</t>
+          <t>3.07% (148.1)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4881.4</v>
+        <v>4975.9</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4947.3</v>
+        <v>5124</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1088,15 +1088,15 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1656</v>
+        <v>1634.8</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 13:00</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
@@ -1109,14 +1109,14 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.61% (10.2)</t>
+          <t>1.88% (31.4)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1676.4</v>
+        <v>1697.6</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1686.6</v>
+        <v>1729</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -1336,35 +1336,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
+          <t>2026-10-15 11:15</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>887</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
           <t>2026-10-14 15:00</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>882.5</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-12 15:15</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>895.4</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-12 12:15</t>
-        </is>
-      </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>1.44% (12.9)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>908.3</v>
+        <v>913.9</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>921.2</v>
+        <v>940.8</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:15</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:45</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -1894,35 +1894,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1743.2</v>
+        <v>1725.5</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 13:00</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1770.7</v>
+        <v>1751.3</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 15:15</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.55% (27.5)</t>
+          <t>1.47% (25.8)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1798.2</v>
+        <v>1777.1</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1825.7</v>
+        <v>1802.9</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -1930,6 +1930,192 @@
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>453.95</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>2.17% (9.85)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>463.8</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>473.65</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1038.1</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>1064.7</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:30</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2.5% (26.6)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1091.3</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>1117.9</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>2559.6</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>2593</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>1.66% (43.0)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>2636</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>2679</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1946,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2293,7 +2479,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2306,35 +2492,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 09:15</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>4749.6</v>
+        <v>4679.7</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13 11:15</t>
+          <t>2026-10-14 13:30</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>4815.5</v>
+        <v>4827.8</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 09:45</t>
+          <t>2026-10-14 11:00</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.37% (65.9)</t>
+          <t>3.07% (148.1)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4881.4</v>
+        <v>4975.9</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>4947.3</v>
+        <v>5124</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -2492,15 +2678,15 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-15 15:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1656</v>
+        <v>1634.8</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 11:45</t>
+          <t>2026-10-14 13:00</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
@@ -2513,14 +2699,14 @@
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.61% (10.2)</t>
+          <t>1.88% (31.4)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1676.4</v>
+        <v>1697.6</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1686.6</v>
+        <v>1729</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -2678,7 +2864,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -2727,7 +2913,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -2740,35 +2926,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
+          <t>2026-10-15 11:15</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>860.1</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>887</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
           <t>2026-10-14 15:00</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>882.5</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-12 15:15</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>895.4</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-12 12:15</t>
-        </is>
-      </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>1.44% (12.9)</t>
+          <t>3.03% (26.9)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>908.3</v>
+        <v>913.9</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>921.2</v>
+        <v>940.8</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -2988,7 +3174,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 13:15</t>
+          <t>2026-10-15 09:15</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -3050,7 +3236,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13 14:45</t>
+          <t>2026-10-15 09:45</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -3298,35 +3484,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-15 09:30</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1743.2</v>
+        <v>1725.5</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 09:30</t>
+          <t>2026-10-14 13:00</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1770.7</v>
+        <v>1751.3</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-13 15:15</t>
+          <t>2026-10-14 11:45</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.55% (27.5)</t>
+          <t>1.47% (25.8)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1798.2</v>
+        <v>1777.1</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1825.7</v>
+        <v>1802.9</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -3334,6 +3520,192 @@
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>446.05</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 09:15</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>453.95</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>2.17% (9.85)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>463.8</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>473.65</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1051.2</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1038.1</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>1064.7</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:30</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2.5% (26.6)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1091.3</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>1117.9</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>2559.6</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:15</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>2593</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>1.66% (43.0)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>2636</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>2679</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -902,7 +902,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 15:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -1212,35 +1212,35 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-16 13:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>835</v>
+        <v>808.75</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>867.5</v>
+        <v>861.95</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>3.75% (32.5)</t>
+          <t>6.17% (53.2)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>900</v>
+        <v>915.15</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>932.5</v>
+        <v>968.35</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
@@ -1956,35 +1956,35 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15 09:15</t>
+          <t>2026-10-16 13:30</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>444.1</v>
+        <v>435.65</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>453.95</v>
+        <v>449.1</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2.17% (9.85)</t>
+          <t>2.99% (13.45)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>463.8</v>
+        <v>462.55</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>473.65</v>
+        <v>476</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-16 09:30</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2116,6 +2116,254 @@
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>230.18</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>225.22</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>233.78</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>3.66% (8.56)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>242.34</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>9113.5</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:45</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>9170.5</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:45</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>2.54% (233.0)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>9403.5</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>9636.5</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2853.5</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>2894.1</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:15</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (50.7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>2944.8</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>2995.5</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:15</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:15</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>1.64% (7.05)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2132,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2492,7 +2740,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 10:00</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
@@ -2678,7 +2926,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15 15:00</t>
+          <t>2026-10-16 15:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -2789,7 +3037,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -2802,35 +3050,35 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-13 13:30</t>
+          <t>2026-10-16 13:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>835</v>
+        <v>808.75</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-13 09:15</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>867.5</v>
+        <v>861.95</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-12 15:15</t>
+          <t>2026-10-14 15:00</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>3.75% (32.5)</t>
+          <t>6.17% (53.2)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>900</v>
+        <v>915.15</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>932.5</v>
+        <v>968.35</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -3484,7 +3732,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 09:30</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -3533,7 +3781,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
@@ -3546,35 +3794,35 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-15 09:15</t>
+          <t>2026-10-16 13:30</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>444.1</v>
+        <v>435.65</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-14 15:00</t>
+          <t>2026-10-16 09:45</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>453.95</v>
+        <v>449.1</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00</t>
+          <t>2026-10-16 09:15</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>2.17% (9.85)</t>
+          <t>2.99% (13.45)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>463.8</v>
+        <v>462.55</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>473.65</v>
+        <v>476</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -3608,7 +3856,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15 10:00</t>
+          <t>2026-10-16 09:30</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -3706,6 +3954,254 @@
         </is>
       </c>
       <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>230.18</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>225.22</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:30</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>233.78</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:00</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>3.66% (8.56)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>242.34</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>250.9</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>9113.5</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-14 10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:45</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>9170.5</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:45</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>2.54% (233.0)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>9403.5</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>9636.5</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2853.5</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 09:30</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>2894.1</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:15</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>1.75% (50.7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>2944.8</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>2995.5</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>VBL</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:45</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>424.05</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:15</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>431.1</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:15</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>1.64% (7.05)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>438.15</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>445.2</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
@@ -716,35 +716,35 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:15</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2310</v>
+        <v>2299</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-21 14:45</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2324.2</v>
+        <v>2341.5</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:15</t>
+          <t>2026-10-21 10:30</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>0.61% (14.2)</t>
+          <t>1.82% (42.5)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2338.4</v>
+        <v>2384</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2352.6</v>
+        <v>2426.5</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -902,35 +902,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-21 11:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>435.05</v>
+        <v>434.75</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-21 09:45</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>438.35</v>
+        <v>438.45</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 09:15</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.75% (3.3)</t>
+          <t>0.84% (3.7)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>441.65</v>
+        <v>442.15</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>444.95</v>
+        <v>445.85</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -964,42 +964,1158 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4533.8</v>
+        <v>4474.6</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>4572.1</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>2.13% (97.5)</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>4669.6</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>4767.1</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1245.6</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1272.2</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2.09% (26.6)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1298.8</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1325.4</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1725.1</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1735.6</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0.64% (11.1)</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>1746.7</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>1757.8</v>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:15</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (2.65)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0.58% (2.15)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>376.05</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:15</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>0.63% (1.04)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>704.5</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:30</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0.85% (6.0)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>710.5</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:45</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2.03% (11.0)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>553.7</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>564.7</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1626.4</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1640.6</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:45</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0.87% (14.2)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1654.8</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1669</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4615</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>4585</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>4634.2</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (49.2)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4683.4</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>4732.6</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>831.25</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:30</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>853.7</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:30</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>2.63% (22.45)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>876.15</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>898.6</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:45</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>446.85</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2.43% (10.85)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>468.55</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
           <t>2026-10-19 09:15</t>
         </is>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>4551.2</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-19 14:45</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0.38% (17.4)</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>4568.6</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>4586</v>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:15</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1.75% (1.26)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1465.7</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>0.37% (5.4)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1471.1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1476.5</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.47% (1.4)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1721.7</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1725.9</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:00</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>0.24% (4.2)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1730.1</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1734.3</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>170.66</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>1.9% (3.31)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>177.28</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>180.59</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4361</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>4351.1</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:00</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>0.32% (14.0)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4379.1</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>4393.1</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>1116.6</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (10.6)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>1127.2</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -1016,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1028,7 +2144,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
@@ -1177,7 +2293,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
@@ -1190,35 +2306,35 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 13:15</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2310</v>
+        <v>2299</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-21 14:45</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2324.2</v>
+        <v>2341.5</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 13:15</t>
+          <t>2026-10-21 10:30</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>0.61% (14.2)</t>
+          <t>1.82% (42.5)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2338.4</v>
+        <v>2384</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2352.6</v>
+        <v>2426.5</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -1363,7 +2479,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -1376,35 +2492,35 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-21 11:15</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>435.05</v>
+        <v>434.75</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-21 09:45</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>438.35</v>
+        <v>438.45</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 09:15</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.75% (3.3)</t>
+          <t>0.84% (3.7)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>441.65</v>
+        <v>442.15</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>444.95</v>
+        <v>445.85</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -1425,7 +2541,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -1438,42 +2554,1158 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4533.8</v>
+        <v>4474.6</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>4572.1</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>2.13% (97.5)</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>4669.6</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>4767.1</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1245.6</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1272.2</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2.09% (26.6)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1298.8</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1325.4</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1725.1</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1724.5</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1735.6</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0.64% (11.1)</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>1746.7</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>1757.8</v>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:15</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>0.72% (2.65)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>374.9</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>372.8</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>0.58% (2.15)</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>376.05</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>165.87</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>165.92</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:15</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>0.63% (1.04)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>166.96</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>700.35</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:00</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>698.5</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>704.5</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:30</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0.85% (6.0)</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>710.5</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>716.5</v>
+      </c>
+      <c r="M13" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>532.6</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>531.7</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:45</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:45</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>2.03% (11.0)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>553.7</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>564.7</v>
+      </c>
+      <c r="M14" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1626.4</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1640.6</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:45</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0.87% (14.2)</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1654.8</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>1669</v>
+      </c>
+      <c r="M15" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>4615</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>4585</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>4634.2</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (49.2)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>4683.4</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>4732.6</v>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>845.7</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>831.25</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:30</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>853.7</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:30</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>2.63% (22.45)</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>876.15</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>898.6</v>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>437.2</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:15</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:45</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>446.85</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 09:15</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2.43% (10.85)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>457.7</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>468.55</v>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
           <t>2026-10-19 09:15</t>
         </is>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>4551.2</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-19 14:45</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>0.38% (17.4)</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>4568.6</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>4586</v>
-      </c>
-      <c r="M7" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:30</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-19 12:15</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:15</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>1.75% (1.26)</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>73.13</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1462</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>1460.3</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1465.7</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>0.37% (5.4)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1471.1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1476.5</v>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 10:15</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>299.1</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>0.47% (1.4)</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>301.9</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>303.3</v>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1725.5</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:15</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:30</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1721.7</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1725.9</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:00</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>0.24% (4.2)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>1730.1</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>1734.3</v>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:30</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>170.66</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>1.9% (3.31)</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>177.28</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>180.59</v>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N23" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4361</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>4351.1</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:15</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>4365.1</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:00</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>0.32% (14.0)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>4379.1</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>4393.1</v>
+      </c>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1107.3</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-21 14:45</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>1116.6</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:45</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>0.95% (10.6)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>1127.2</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>1137.8</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -964,7 +964,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1026,35 +1026,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 12:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1245.6</v>
+        <v>1214.1</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1272.2</v>
+        <v>1259</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2.09% (26.6)</t>
+          <t>3.57% (44.9)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1298.8</v>
+        <v>1303.9</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1325.4</v>
+        <v>1348.8</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -1088,35 +1088,35 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1724.5</v>
+        <v>1715.3</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1735.6</v>
+        <v>1748.8</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.64% (11.1)</t>
+          <t>1.92% (33.5)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1746.7</v>
+        <v>1782.3</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1757.8</v>
+        <v>1815.8</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -1212,35 +1212,35 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>371.75</v>
+        <v>368.5</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>373.9</v>
+        <v>379.05</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:00</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0.58% (2.15)</t>
+          <t>2.78% (10.55)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>376.05</v>
+        <v>389.6</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>378.2</v>
+        <v>400.15</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 13:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -1336,35 +1336,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>698.5</v>
+        <v>691.65</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 10:00</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>704.5</v>
+        <v>706.95</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0.85% (6.0)</t>
+          <t>2.16% (15.3)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>710.5</v>
+        <v>722.25</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>716.5</v>
+        <v>737.55</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1398,35 +1398,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:15</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>531.7</v>
+        <v>528.9</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>542.7</v>
+        <v>539.65</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.03% (11.0)</t>
+          <t>1.99% (10.75)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>553.7</v>
+        <v>550.4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>564.7</v>
+        <v>561.15</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -1460,35 +1460,35 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 13:45</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1626.4</v>
+        <v>1616.6</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1640.6</v>
+        <v>1644.9</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0.87% (14.2)</t>
+          <t>1.72% (28.3)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1654.8</v>
+        <v>1673.2</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1669</v>
+        <v>1701.5</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1522,35 +1522,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4585</v>
+        <v>4548.9</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4634.2</v>
+        <v>4641.5</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.06% (49.2)</t>
+          <t>2.0% (92.6)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4683.4</v>
+        <v>4734.1</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4732.6</v>
+        <v>4826.7</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1646,35 +1646,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:45</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>436</v>
+        <v>433.75</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>446.85</v>
+        <v>438.2</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.43% (10.85)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>457.7</v>
+        <v>442.65</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>468.55</v>
+        <v>447.1</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -1770,35 +1770,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:45</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1460.3</v>
+        <v>1451</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1465.7</v>
+        <v>1484.9</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>0.37% (5.4)</t>
+          <t>2.28% (33.9)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1471.1</v>
+        <v>1518.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1476.5</v>
+        <v>1552.7</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
@@ -1832,35 +1832,35 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:00</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>299.1</v>
+        <v>295.55</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>300.5</v>
+        <v>302.5</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0.47% (1.4)</t>
+          <t>2.3% (6.95)</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>301.9</v>
+        <v>309.45</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>303.3</v>
+        <v>316.4</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -1876,53 +1876,53 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1725.5</v>
+        <v>1634.5</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-22 14:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1721.7</v>
+        <v>1620</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1725.9</v>
+        <v>1667.3</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:00</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>0.24% (4.2)</t>
+          <t>2.84% (47.3)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1730.1</v>
+        <v>1714.6</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1734.3</v>
+        <v>1761.9</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -1938,53 +1938,53 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>171.66</v>
+        <v>1725.5</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-21 12:15</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1719.6</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>1745.1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
           <t>2026-10-21 15:15</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>170.66</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>173.97</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00</t>
-        </is>
-      </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>1.9% (3.31)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>177.28</v>
+        <v>1770.6</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>180.59</v>
+        <v>1796.1</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2000,53 +2000,53 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4361</v>
+        <v>171.66</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-21 13:30</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 15:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4351.1</v>
+        <v>168.11</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>4365.1</v>
+        <v>172.45</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:00</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.32% (14.0)</t>
+          <t>2.52% (4.34)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4379.1</v>
+        <v>176.79</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4393.1</v>
+        <v>181.13</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2062,60 +2062,866 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>4361</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>4329.2</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>4380.9</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>1.18% (51.7)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>4432.6</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>4484.3</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>1107.3</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>2026-10-21 14:45</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1106</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1116.6</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:45</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>0.95% (10.6)</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>1127.2</v>
-      </c>
-      <c r="L25" s="13" t="n">
-        <v>1137.8</v>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1100.3</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>1117.3</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (17.0)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>1151.3</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>277</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:45</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>288</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>3.82% (11.0)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>299</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>310</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>821.75</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>1.62% (13.35)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>848.45</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1314</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>1.32% (17.3)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2.88% (11.75)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>431</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2828.2</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>2.11% (60.9)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>2950</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>3010.9</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1814.4</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1810.6</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1822.3</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.7)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1834</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1845.7</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>260.35</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>1.5% (3.9)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>268.15</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1001.4</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>1028</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (26.6)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1054.6</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>11125</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>10990</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>1.88% (210.0)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>11410</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>11620</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>152.77</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:30</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:15</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:00</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>1.95% (3.03)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>158.46</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>161.49</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>245</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>252.15</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>2.91% (7.35)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>266.85</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>949.5</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>970.65</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2.18% (21.15)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1012.95</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2132,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2554,7 +3360,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -2603,7 +3409,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2616,35 +3422,35 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 12:45</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1245.6</v>
+        <v>1214.1</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1272.2</v>
+        <v>1259</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2.09% (26.6)</t>
+          <t>3.57% (44.9)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1298.8</v>
+        <v>1303.9</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1325.4</v>
+        <v>1348.8</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -2665,7 +3471,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -2678,35 +3484,35 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:00</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1724.5</v>
+        <v>1715.3</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1735.6</v>
+        <v>1748.8</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0.64% (11.1)</t>
+          <t>1.92% (33.5)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1746.7</v>
+        <v>1782.3</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1757.8</v>
+        <v>1815.8</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -2789,7 +3595,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -2802,35 +3608,35 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:00</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>371.75</v>
+        <v>368.5</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>373.9</v>
+        <v>379.05</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:00</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0.58% (2.15)</t>
+          <t>2.78% (10.55)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>376.05</v>
+        <v>389.6</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>378.2</v>
+        <v>400.15</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -2864,7 +3670,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 13:30</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
@@ -2913,7 +3719,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -2926,35 +3732,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>698.5</v>
+        <v>691.65</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 10:00</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>704.5</v>
+        <v>706.95</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0.85% (6.0)</t>
+          <t>2.16% (15.3)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>710.5</v>
+        <v>722.25</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>716.5</v>
+        <v>737.55</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -2975,7 +3781,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -2988,35 +3794,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:15</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>531.7</v>
+        <v>528.9</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>542.7</v>
+        <v>539.65</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.03% (11.0)</t>
+          <t>1.99% (10.75)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>553.7</v>
+        <v>550.4</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>564.7</v>
+        <v>561.15</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -3037,7 +3843,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -3050,35 +3856,35 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 13:45</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1626.4</v>
+        <v>1616.6</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1640.6</v>
+        <v>1644.9</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>0.87% (14.2)</t>
+          <t>1.72% (28.3)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1654.8</v>
+        <v>1673.2</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1669</v>
+        <v>1701.5</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -3099,7 +3905,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -3112,35 +3918,35 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 10:45</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4585</v>
+        <v>4548.9</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4634.2</v>
+        <v>4641.5</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 12:45</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.06% (49.2)</t>
+          <t>2.0% (92.6)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4683.4</v>
+        <v>4734.1</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4732.6</v>
+        <v>4826.7</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -3174,7 +3980,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -3223,7 +4029,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -3236,35 +4042,35 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:45</t>
+          <t>2026-10-22 14:30</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>436</v>
+        <v>433.75</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 11:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>446.85</v>
+        <v>438.2</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.43% (10.85)</t>
+          <t>1.02% (4.45)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>457.7</v>
+        <v>442.65</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>468.55</v>
+        <v>447.1</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -3347,7 +4153,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -3360,35 +4166,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 11:45</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1460.3</v>
+        <v>1451</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1465.7</v>
+        <v>1484.9</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>0.37% (5.4)</t>
+          <t>2.28% (33.9)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1471.1</v>
+        <v>1518.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1476.5</v>
+        <v>1552.7</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -3409,7 +4215,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
@@ -3422,35 +4228,35 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:00</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>299.1</v>
+        <v>295.55</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>300.5</v>
+        <v>302.5</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>0.47% (1.4)</t>
+          <t>2.3% (6.95)</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>301.9</v>
+        <v>309.45</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>303.3</v>
+        <v>316.4</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -3466,53 +4272,53 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1725.5</v>
+        <v>1634.5</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-22 14:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1721.7</v>
+        <v>1620</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:45</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1725.9</v>
+        <v>1667.3</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:00</t>
+          <t>2026-10-21 15:00</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>0.24% (4.2)</t>
+          <t>2.84% (47.3)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1730.1</v>
+        <v>1714.6</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1734.3</v>
+        <v>1761.9</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -3528,53 +4334,53 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>171.66</v>
+        <v>1725.5</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-21 12:15</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>1719.6</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>1745.1</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
           <t>2026-10-21 15:15</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n">
-        <v>170.66</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>173.97</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00</t>
-        </is>
-      </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>1.9% (3.31)</t>
+          <t>1.46% (25.5)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>177.28</v>
+        <v>1770.6</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>180.59</v>
+        <v>1796.1</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -3590,53 +4396,53 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4361</v>
+        <v>171.66</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-21 13:30</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-22 15:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>4351.1</v>
+        <v>168.11</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>4365.1</v>
+        <v>172.45</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 14:00</t>
+          <t>2026-10-21 15:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.32% (14.0)</t>
+          <t>2.52% (4.34)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4379.1</v>
+        <v>176.79</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>4393.1</v>
+        <v>181.13</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -3652,60 +4458,866 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>4361</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:00</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:15</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>4329.2</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>4380.9</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>1.18% (51.7)</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>4432.6</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>4484.3</v>
+      </c>
+      <c r="M25" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N25" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
         <v>1107.3</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>2026-10-21 14:45</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>1106</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-21 14:45</t>
-        </is>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1116.6</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 12:45</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>0.95% (10.6)</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>1127.2</v>
-      </c>
-      <c r="L25" s="13" t="n">
-        <v>1137.8</v>
-      </c>
-      <c r="M25" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>1100.3</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>1117.3</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>1.52% (17.0)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>1134.3</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>1151.3</v>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>277</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:45</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>288</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>3.82% (11.0)</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>299</v>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>310</v>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>808.55</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>808.4</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 10:00</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>821.75</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:00</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>1.62% (13.35)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>835.1</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>848.45</v>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>1300.2</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1314</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>1.32% (17.3)</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>1331.3</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>395.75</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>2.88% (11.75)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>431</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>2843.4</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2828.2</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>2889.1</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>2.11% (60.9)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>2950</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>3010.9</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1814.4</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1810.6</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1822.3</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>0.64% (11.7)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1834</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1845.7</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>260.35</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>1.5% (3.9)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>264.25</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>268.15</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>1001.4</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>1028</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (26.6)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1054.6</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>1081.2</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>11125</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>10990</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>1.88% (210.0)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>11410</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>11620</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>152.77</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:00</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:30</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:15</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>155.43</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 11:00</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>1.95% (3.03)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>158.46</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>161.49</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>245</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>244.8</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>252.15</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>2.91% (7.35)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>266.85</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>953.2</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:45</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>949.5</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:15</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>970.65</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-21 15:15</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2.18% (21.15)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>991.8</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1012.95</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
@@ -654,35 +654,35 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-23 14:30</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7677</v>
+        <v>7468</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>7729</v>
+        <v>7705</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 10:45</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>3.08% (237.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>7781</v>
+        <v>7942</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>7833</v>
+        <v>8179</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45</t>
+          <t>2026-10-23 13:00</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -1894,35 +1894,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:15</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-23 13:15</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1667.3</v>
+        <v>1647.5</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-23 09:45</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.84% (47.3)</t>
+          <t>2.34% (38.5)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1714.6</v>
+        <v>1686</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1761.9</v>
+        <v>1724.5</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2266,15 +2266,15 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>808.4</v>
+        <v>772.5</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 10:15</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -2282,19 +2282,19 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:45</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.62% (13.35)</t>
+          <t>5.99% (49.25)</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>835.1</v>
+        <v>871</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>848.45</v>
+        <v>920.25</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -2514,35 +2514,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1810.6</v>
+        <v>1781.1</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00</t>
+          <t>2026-10-23 13:15</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1822.3</v>
+        <v>1834.9</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>2.93% (53.8)</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1834</v>
+        <v>1888.7</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1845.7</v>
+        <v>1942.5</v>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
@@ -2576,35 +2576,35 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>256.45</v>
+        <v>254.85</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00</t>
+          <t>2026-10-23 11:45</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>260.35</v>
+        <v>257.05</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-23 11:15</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>1.5% (3.9)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>264.25</v>
+        <v>259.25</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>268.15</v>
+        <v>261.45</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-23 13:45</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
@@ -2824,35 +2824,35 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 14:45</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>244.8</v>
+        <v>242.3</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 12:00</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>252.15</v>
+        <v>248.4</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 15:15</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2.91% (7.35)</t>
+          <t>2.46% (6.1)</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>259.5</v>
+        <v>254.5</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>266.85</v>
+        <v>260.6</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -2886,35 +2886,35 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>949.5</v>
+        <v>948.9</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 12:30</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>970.65</v>
+        <v>961.4</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-23 10:30</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.18% (21.15)</t>
+          <t>1.3% (12.5)</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>991.8</v>
+        <v>973.9</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1012.95</v>
+        <v>986.4</v>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -2922,6 +2922,378 @@
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8797.5</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>8946.5</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:15</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>1.67% (149.0)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>9095.5</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>9244.5</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>7008.5</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>6918</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>7084.5</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2.35% (166.5)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7251</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>7417.5</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>840.5</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:45</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>837.3</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:15</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>846</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:30</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>1.03% (8.7)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>854.7</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>857.15</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:15</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>852</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>4.25% (37.8)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>927.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>965.4</v>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:45</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:15</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>1605.1</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1694</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>5.25% (88.9)</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1782.9</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1871.8</v>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:00</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (4.85)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2938,7 +3310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3037,7 +3409,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
@@ -3050,35 +3422,35 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-23 14:30</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7677</v>
+        <v>7468</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-22 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>7729</v>
+        <v>7705</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-21 10:45</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>0.67% (52.0)</t>
+          <t>3.08% (237.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>7781</v>
+        <v>7942</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>7833</v>
+        <v>8179</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -3484,7 +3856,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -4104,7 +4476,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30</t>
+          <t>2026-10-23 09:30</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -4166,7 +4538,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:45</t>
+          <t>2026-10-23 13:00</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
@@ -4277,7 +4649,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -4290,35 +4662,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:15</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1620</v>
+        <v>1609</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-23 13:15</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1667.3</v>
+        <v>1647.5</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-23 09:45</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.84% (47.3)</t>
+          <t>2.34% (38.5)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1714.6</v>
+        <v>1686</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1761.9</v>
+        <v>1724.5</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -4649,7 +5021,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -4662,15 +5034,15 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>808.4</v>
+        <v>772.5</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-23 10:15</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
@@ -4678,19 +5050,19 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-22 14:45</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.62% (13.35)</t>
+          <t>5.99% (49.25)</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>835.1</v>
+        <v>871</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>848.45</v>
+        <v>920.25</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -4897,7 +5269,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
@@ -4910,35 +5282,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1810.6</v>
+        <v>1781.1</v>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 15:00</t>
+          <t>2026-10-23 13:15</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1822.3</v>
+        <v>1834.9</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-23 09:15</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>0.64% (11.7)</t>
+          <t>2.93% (53.8)</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>1834</v>
+        <v>1888.7</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>1845.7</v>
+        <v>1942.5</v>
       </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
@@ -4959,7 +5331,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
@@ -4972,35 +5344,35 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00</t>
+          <t>2026-10-23 15:00</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>256.45</v>
+        <v>254.85</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 12:00</t>
+          <t>2026-10-23 11:45</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>260.35</v>
+        <v>257.05</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-23 11:15</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>1.5% (3.9)</t>
+          <t>0.86% (2.2)</t>
         </is>
       </c>
       <c r="K33" s="13" t="n">
-        <v>264.25</v>
+        <v>259.25</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>268.15</v>
+        <v>261.45</v>
       </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
@@ -5096,7 +5468,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-23 13:45</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -5207,7 +5579,7 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
@@ -5220,35 +5592,35 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 14:45</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>244.8</v>
+        <v>242.3</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 12:00</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>252.15</v>
+        <v>248.4</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-22 15:15</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>2.91% (7.35)</t>
+          <t>2.46% (6.1)</t>
         </is>
       </c>
       <c r="K37" s="13" t="n">
-        <v>259.5</v>
+        <v>254.5</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>266.85</v>
+        <v>260.6</v>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
@@ -5269,7 +5641,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -5282,35 +5654,35 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-23 15:15</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>949.5</v>
+        <v>948.9</v>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-23 12:30</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>970.65</v>
+        <v>961.4</v>
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-23 10:30</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.18% (21.15)</t>
+          <t>1.3% (12.5)</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>991.8</v>
+        <v>973.9</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>1012.95</v>
+        <v>986.4</v>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
@@ -5318,6 +5690,378 @@
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>8937.5</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:15</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>8797.5</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>8946.5</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:15</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>1.67% (149.0)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>9095.5</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>9244.5</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>7008.5</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 15:00</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>6918</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>7084.5</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:15</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>2.35% (166.5)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>7251</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>7417.5</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>840.5</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:45</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>837.3</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:15</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>846</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:30</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>1.03% (8.7)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>854.7</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>863.4</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>857.15</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:15</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>852</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:30</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>889.8</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>4.25% (37.8)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>927.6</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>965.4</v>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>1636.2</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 09:45</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-23 14:15</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>1605.1</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:15</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1694</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-22 15:00</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>5.25% (88.9)</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1782.9</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1871.8</v>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>340.7</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:45</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>345.25</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:00</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.4% (4.85)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,53 +636,53 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>7688</v>
+        <v>6070</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7468</v>
+        <v>6065</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>7705</v>
+        <v>6152</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>3.08% (237.0)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>7942</v>
+        <v>6239</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>8179</v>
+        <v>6326</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -698,53 +698,53 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>2317.8</v>
+        <v>2462.1</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2299</v>
+        <v>2447.8</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2341.5</v>
+        <v>2481</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>1.82% (42.5)</t>
+          <t>1.34% (33.2)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2384</v>
+        <v>2514.2</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2426.5</v>
+        <v>2547.4</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -760,53 +760,53 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>426.15</v>
+        <v>2260</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>425.6</v>
+        <v>2234.3</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>432.8</v>
+        <v>2283.3</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.66% (7.2)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>440</v>
+        <v>2332.3</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>447.2</v>
+        <v>2381.3</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -822,53 +822,53 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>4591.2</v>
+        <v>907.4</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4587</v>
+        <v>906.55</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4610</v>
+        <v>920.6</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>1.53% (14.05)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>4633</v>
+        <v>934.65</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>4656</v>
+        <v>948.7</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -884,53 +884,53 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>435.2</v>
+        <v>229.2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 13:30</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>434.75</v>
+        <v>227.3</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>438.45</v>
+        <v>229.7</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-26 13:30</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.84% (3.7)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>442.15</v>
+        <v>232.1</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>445.85</v>
+        <v>234.5</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -946,53 +946,53 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4550.4</v>
+        <v>4515</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4474.6</v>
+        <v>4507.9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4572.1</v>
+        <v>4540.1</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4669.6</v>
+        <v>4572.3</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>4767.1</v>
+        <v>4604.5</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1008,53 +1008,53 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1255.4</v>
+        <v>115.37</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:45</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1214.1</v>
+        <v>114.72</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1259</v>
+        <v>115.75</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>3.57% (44.9)</t>
+          <t>0.89% (1.03)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1303.9</v>
+        <v>116.78</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1348.8</v>
+        <v>117.81</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -1070,53 +1070,53 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1725.1</v>
+        <v>4716.3</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1715.3</v>
+        <v>4642.1</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1748.8</v>
+        <v>4733</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>1.92% (33.5)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1782.3</v>
+        <v>4823.9</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1815.8</v>
+        <v>4914.8</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -1132,53 +1132,53 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>369.4</v>
+        <v>686.85</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-26 11:30</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 15:00</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>366.95</v>
+        <v>684</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-26 13:45</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>369.6</v>
+        <v>690</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:15</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.72% (2.65)</t>
+          <t>0.87% (6.0)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>372.25</v>
+        <v>696</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>374.9</v>
+        <v>702</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1194,53 +1194,53 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>372.8</v>
+        <v>4994.5</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>368.5</v>
+        <v>4977.5</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>379.05</v>
+        <v>5054.5</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.78% (10.55)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>389.6</v>
+        <v>5131.5</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>400.15</v>
+        <v>5208.5</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1256,53 +1256,53 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>165.87</v>
+        <v>852</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>164.88</v>
+        <v>851.35</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>165.92</v>
+        <v>864</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>166.96</v>
+        <v>876.65</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>168</v>
+        <v>889.3</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -1318,53 +1318,53 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>700.35</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>691.65</v>
+        <v>73.22</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>706.95</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.16% (15.3)</t>
+          <t>2.18% (1.63)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>722.25</v>
+        <v>76.48</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>737.55</v>
+        <v>78.11</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1380,53 +1380,53 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>532.6</v>
+        <v>254.8</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>528.9</v>
+        <v>254.5</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>539.65</v>
+        <v>256.25</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.99% (10.75)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>550.4</v>
+        <v>258</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>561.15</v>
+        <v>259.75</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -1442,53 +1442,53 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1631</v>
+        <v>440.15</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1616.6</v>
+        <v>440.15</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1644.9</v>
+        <v>446.35</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>1.72% (28.3)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1673.2</v>
+        <v>452.55</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1701.5</v>
+        <v>458.75</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -1504,53 +1504,53 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4615</v>
+        <v>941</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4548.9</v>
+        <v>939.8</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4641.5</v>
+        <v>948.2</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.0% (92.6)</t>
+          <t>0.89% (8.4)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4734.1</v>
+        <v>956.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4826.7</v>
+        <v>965</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -1566,53 +1566,53 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>845.7</v>
+        <v>1845</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>831.25</v>
+        <v>1838.7</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>853.7</v>
+        <v>1860.9</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:30</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.63% (22.45)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>876.15</v>
+        <v>1883.1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>898.6</v>
+        <v>1905.3</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -1628,53 +1628,53 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>437.2</v>
+        <v>148.07</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>433.75</v>
+        <v>147.32</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>438.2</v>
+        <v>148.9</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>442.65</v>
+        <v>150.48</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>447.1</v>
+        <v>152.06</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -1690,53 +1690,53 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>71.44</v>
+        <v>1177.6</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>70.61</v>
+        <v>1169.8</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>71.87</v>
+        <v>1188.2</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>1.75% (1.26)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>73.13</v>
+        <v>1206.6</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>74.39</v>
+        <v>1225</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -1752,53 +1752,53 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1462</v>
+        <v>69.03</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1451</v>
+        <v>68.84</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1484.9</v>
+        <v>69.33</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.28% (33.9)</t>
+          <t>0.71% (0.49)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1518.8</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1552.7</v>
+        <v>70.31</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -1814,53 +1814,53 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>300</v>
+        <v>444.9</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>295.55</v>
+        <v>441.7</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>302.5</v>
+        <v>447.5</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.3% (6.95)</t>
+          <t>1.3% (5.8)</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>309.45</v>
+        <v>453.3</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>316.4</v>
+        <v>459.1</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -1876,53 +1876,53 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1634.5</v>
+        <v>312.75</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1609</v>
+        <v>310.5</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23 13:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1647.5</v>
+        <v>313.9</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.34% (38.5)</t>
+          <t>1.08% (3.4)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1686</v>
+        <v>317.3</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1724.5</v>
+        <v>320.7</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -1938,53 +1938,53 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1725.5</v>
+        <v>119.06</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:30</t>
+          <t>2026-10-26 12:45</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1719.6</v>
+        <v>118.25</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1745.1</v>
+        <v>119.24</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 12:45</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>0.83% (0.99)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>1770.6</v>
+        <v>120.23</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>1796.1</v>
+        <v>121.22</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -2000,53 +2000,53 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>171.66</v>
+        <v>290.65</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>168.11</v>
+        <v>289.5</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>172.45</v>
+        <v>291.8</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.52% (4.34)</t>
+          <t>0.79% (2.3)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>176.79</v>
+        <v>294.1</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>181.13</v>
+        <v>296.4</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2062,53 +2062,53 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>4361</v>
+        <v>949.95</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-26 11:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4329.2</v>
+        <v>943.5</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>4380.9</v>
+        <v>958</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>1.18% (51.7)</t>
+          <t>1.51% (14.5)</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>4432.6</v>
+        <v>972.5</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>4484.3</v>
+        <v>987</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -2124,53 +2124,53 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1107.3</v>
+        <v>4470.4</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1100.3</v>
+        <v>4467.3</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1117.3</v>
+        <v>4565</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>1134.3</v>
+        <v>4662.7</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1151.3</v>
+        <v>4760.4</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -2186,53 +2186,53 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>283.25</v>
+        <v>3898.1</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>277</v>
+        <v>3875.1</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>288</v>
+        <v>3961.9</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>3.82% (11.0)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>299</v>
+        <v>4048.7</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>310</v>
+        <v>4135.5</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -2248,53 +2248,53 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>808.55</v>
+        <v>223.35</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>772.5</v>
+        <v>221.8</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>821.75</v>
+        <v>225</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>5.99% (49.25)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>871</v>
+        <v>228.2</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>920.25</v>
+        <v>231.4</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -2310,53 +2310,53 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1300.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:30</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1296.7</v>
+        <v>1094</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1314</v>
+        <v>1158.5</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 10:00</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>1331.3</v>
+        <v>1223</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1348.6</v>
+        <v>1287.5</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -2364,936 +2364,6 @@
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>402.1</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>395.75</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>407.5</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>2.88% (11.75)</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>431</v>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>2843.4</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>2828.2</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>2889.1</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>2.11% (60.9)</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>2950</v>
-      </c>
-      <c r="L31" s="13" t="n">
-        <v>3010.9</v>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N31" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>1814.4</v>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 14:45</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1781.1</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1834.9</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>2.93% (53.8)</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>1888.7</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>1942.5</v>
-      </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>256.95</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:00</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:00</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>254.85</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:45</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>257.05</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:15</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>0.86% (2.2)</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>261.45</v>
-      </c>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>1003.5</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>1001.4</v>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1028</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>2.59% (26.6)</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>1054.6</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>1081.2</v>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>11125</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:45</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>10990</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>11200</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>1.88% (210.0)</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>11410</v>
-      </c>
-      <c r="L35" s="13" t="n">
-        <v>11620</v>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>152.77</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:00</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:30</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>152.4</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:15</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>155.43</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 11:00</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>1.95% (3.03)</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>158.46</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>161.49</v>
-      </c>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>245</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 14:45</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>242.3</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:00</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>2.46% (6.1)</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="L37" s="13" t="n">
-        <v>260.6</v>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N37" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>953.2</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>948.9</v>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:30</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>961.4</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>1.3% (12.5)</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>973.9</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>986.4</v>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>8937.5</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>8797.5</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>8946.5</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:15</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>1.67% (149.0)</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>9095.5</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>9244.5</v>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>7008.5</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:00</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>6918</v>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:15</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>7084.5</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>2.35% (166.5)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>7251</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>7417.5</v>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:45</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>837.3</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:15</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>846</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:30</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>1.03% (8.7)</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>854.7</v>
-      </c>
-      <c r="L41" s="13" t="n">
-        <v>863.4</v>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>857.15</v>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:00</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:15</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>852</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>889.8</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 14:30</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>4.25% (37.8)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>927.6</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>965.4</v>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>1636.2</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:45</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 14:15</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>1605.1</v>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>1694</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:00</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>5.25% (88.9)</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>1782.9</v>
-      </c>
-      <c r="L43" s="13" t="n">
-        <v>1871.8</v>
-      </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N43" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>340.7</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>345.25</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:00</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>1.4% (4.85)</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>354.95</v>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -3310,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3404,53 +2474,53 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C2" s="5" t="n">
-        <v>7688</v>
+        <v>6070</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 14:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>7468</v>
+        <v>6065</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H2" s="8" t="n">
-        <v>7705</v>
+        <v>6152</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>3.08% (237.0)</t>
+          <t>1.41% (87.0)</t>
         </is>
       </c>
       <c r="K2" s="5" t="n">
-        <v>7942</v>
+        <v>6239</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>8179</v>
+        <v>6326</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
@@ -3466,53 +2536,53 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
-        <v>2317.8</v>
+        <v>2462.1</v>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2299</v>
+        <v>2447.8</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2341.5</v>
+        <v>2481</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>1.82% (42.5)</t>
+          <t>1.34% (33.2)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2384</v>
+        <v>2514.2</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2426.5</v>
+        <v>2547.4</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -3528,53 +2598,53 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>426.15</v>
+        <v>2260</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>425.6</v>
+        <v>2234.3</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>432.8</v>
+        <v>2283.3</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.66% (7.2)</t>
+          <t>2.15% (49.0)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>440</v>
+        <v>2332.3</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>447.2</v>
+        <v>2381.3</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -3590,53 +2660,53 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>4591.2</v>
+        <v>907.4</v>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4587</v>
+        <v>906.55</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4610</v>
+        <v>920.6</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 11:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0.5% (23.0)</t>
+          <t>1.53% (14.05)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>4633</v>
+        <v>934.65</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>4656</v>
+        <v>948.7</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -3652,53 +2722,53 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>435.2</v>
+        <v>229.2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 13:30</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>434.75</v>
+        <v>227.3</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>438.45</v>
+        <v>229.7</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-26 13:30</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>0.84% (3.7)</t>
+          <t>1.04% (2.4)</t>
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>442.15</v>
+        <v>232.1</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>445.85</v>
+        <v>234.5</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -3714,53 +2784,53 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>4550.4</v>
+        <v>4515</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4474.6</v>
+        <v>4507.9</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4572.1</v>
+        <v>4540.1</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>2.13% (97.5)</t>
+          <t>0.71% (32.2)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4669.6</v>
+        <v>4572.3</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>4767.1</v>
+        <v>4604.5</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -3776,53 +2846,53 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1255.4</v>
+        <v>115.37</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 12:45</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1214.1</v>
+        <v>114.72</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1259</v>
+        <v>115.75</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>3.57% (44.9)</t>
+          <t>0.89% (1.03)</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1303.9</v>
+        <v>116.78</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1348.8</v>
+        <v>117.81</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -3838,53 +2908,53 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1725.1</v>
+        <v>4716.3</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1715.3</v>
+        <v>4642.1</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1748.8</v>
+        <v>4733</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>1.92% (33.5)</t>
+          <t>1.92% (90.9)</t>
         </is>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1782.3</v>
+        <v>4823.9</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1815.8</v>
+        <v>4914.8</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -3900,53 +2970,53 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>369.4</v>
+        <v>686.85</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-26 11:30</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 15:00</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>366.95</v>
+        <v>684</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:15</t>
+          <t>2026-10-26 13:45</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>369.6</v>
+        <v>690</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:15</t>
+          <t>2026-10-26 13:15</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.72% (2.65)</t>
+          <t>0.87% (6.0)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>372.25</v>
+        <v>696</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>374.9</v>
+        <v>702</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -3962,53 +3032,53 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>372.8</v>
+        <v>4994.5</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>368.5</v>
+        <v>4977.5</v>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>379.05</v>
+        <v>5054.5</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>2.78% (10.55)</t>
+          <t>1.52% (77.0)</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
-        <v>389.6</v>
+        <v>5131.5</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>400.15</v>
+        <v>5208.5</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -4024,53 +3094,53 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>165.87</v>
+        <v>852</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>164.88</v>
+        <v>851.35</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>165.92</v>
+        <v>864</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 13:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>0.63% (1.04)</t>
+          <t>1.46% (12.65)</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>166.96</v>
+        <v>876.65</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>168</v>
+        <v>889.3</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
@@ -4086,53 +3156,53 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>700.35</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 13:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>691.65</v>
+        <v>73.22</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>706.95</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.16% (15.3)</t>
+          <t>2.18% (1.63)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>722.25</v>
+        <v>76.48</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>737.55</v>
+        <v>78.11</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -4148,53 +3218,53 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>532.6</v>
+        <v>254.8</v>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>528.9</v>
+        <v>254.5</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>539.65</v>
+        <v>256.25</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.99% (10.75)</t>
+          <t>0.68% (1.75)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>550.4</v>
+        <v>258</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>561.15</v>
+        <v>259.75</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -4210,53 +3280,53 @@
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>1631</v>
+        <v>440.15</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 13:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1616.6</v>
+        <v>440.15</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1644.9</v>
+        <v>446.35</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J15" s="11" t="inlineStr">
         <is>
-          <t>1.72% (28.3)</t>
+          <t>1.39% (6.2)</t>
         </is>
       </c>
       <c r="K15" s="13" t="n">
-        <v>1673.2</v>
+        <v>452.55</v>
       </c>
       <c r="L15" s="13" t="n">
-        <v>1701.5</v>
+        <v>458.75</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
@@ -4272,53 +3342,53 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4615</v>
+        <v>941</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>4548.9</v>
+        <v>939.8</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>4641.5</v>
+        <v>948.2</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.0% (92.6)</t>
+          <t>0.89% (8.4)</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4734.1</v>
+        <v>956.6</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4826.7</v>
+        <v>965</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
@@ -4334,53 +3404,53 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>845.7</v>
+        <v>1845</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>831.25</v>
+        <v>1838.7</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-21 12:30</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>853.7</v>
+        <v>1860.9</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 10:30</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>2.63% (22.45)</t>
+          <t>1.19% (22.2)</t>
         </is>
       </c>
       <c r="K17" s="13" t="n">
-        <v>876.15</v>
+        <v>1883.1</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>898.6</v>
+        <v>1905.3</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
@@ -4396,53 +3466,53 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>437.2</v>
+        <v>148.07</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 11:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 14:30</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>433.75</v>
+        <v>147.32</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>438.2</v>
+        <v>148.9</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.02% (4.45)</t>
+          <t>1.06% (1.58)</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>442.65</v>
+        <v>150.48</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>447.1</v>
+        <v>152.06</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
@@ -4458,53 +3528,53 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>71.44</v>
+        <v>1177.6</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-23 09:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>70.61</v>
+        <v>1169.8</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>71.87</v>
+        <v>1188.2</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-19 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>1.75% (1.26)</t>
+          <t>1.55% (18.4)</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>73.13</v>
+        <v>1206.6</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>74.39</v>
+        <v>1225</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -4520,53 +3590,53 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1462</v>
+        <v>69.03</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 13:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1451</v>
+        <v>68.84</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1484.9</v>
+        <v>69.33</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.28% (33.9)</t>
+          <t>0.71% (0.49)</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>1518.8</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1552.7</v>
+        <v>70.31</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
@@ -4582,53 +3652,53 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>300</v>
+        <v>444.9</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 14:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>295.55</v>
+        <v>441.7</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>302.5</v>
+        <v>447.5</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2.3% (6.95)</t>
+          <t>1.3% (5.8)</t>
         </is>
       </c>
       <c r="K21" s="13" t="n">
-        <v>309.45</v>
+        <v>453.3</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>316.4</v>
+        <v>459.1</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
@@ -4644,53 +3714,53 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1634.5</v>
+        <v>312.75</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1609</v>
+        <v>310.5</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23 13:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1647.5</v>
+        <v>313.9</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 09:45</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.34% (38.5)</t>
+          <t>1.08% (3.4)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>1686</v>
+        <v>317.3</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1724.5</v>
+        <v>320.7</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -4706,53 +3776,53 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>1725.5</v>
+        <v>119.06</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:30</t>
+          <t>2026-10-26 12:45</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1719.6</v>
+        <v>118.25</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1745.1</v>
+        <v>119.24</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 12:45</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>1.46% (25.5)</t>
+          <t>0.83% (0.99)</t>
         </is>
       </c>
       <c r="K23" s="13" t="n">
-        <v>1770.6</v>
+        <v>120.23</v>
       </c>
       <c r="L23" s="13" t="n">
-        <v>1796.1</v>
+        <v>121.22</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
@@ -4768,53 +3838,53 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>171.66</v>
+        <v>290.65</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 13:30</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>168.11</v>
+        <v>289.5</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>172.45</v>
+        <v>291.8</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.52% (4.34)</t>
+          <t>0.79% (2.3)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>176.79</v>
+        <v>294.1</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>181.13</v>
+        <v>296.4</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -4830,53 +3900,53 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>4361</v>
+        <v>949.95</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-21 12:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 11:15</t>
+          <t>2026-10-26 11:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4329.2</v>
+        <v>943.5</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>4380.9</v>
+        <v>958</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>1.18% (51.7)</t>
+          <t>1.51% (14.5)</t>
         </is>
       </c>
       <c r="K25" s="13" t="n">
-        <v>4432.6</v>
+        <v>972.5</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>4484.3</v>
+        <v>987</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
@@ -4892,53 +3962,53 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1107.3</v>
+        <v>4470.4</v>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21 14:45</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1100.3</v>
+        <v>4467.3</v>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:45</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1117.3</v>
+        <v>4565</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:30</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.52% (17.0)</t>
+          <t>2.14% (97.7)</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>1134.3</v>
+        <v>4662.7</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1151.3</v>
+        <v>4760.4</v>
       </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
@@ -4954,53 +4024,53 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>283.25</v>
+        <v>3898.1</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>277</v>
+        <v>3875.1</v>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>288</v>
+        <v>3961.9</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>3.82% (11.0)</t>
+          <t>2.19% (86.8)</t>
         </is>
       </c>
       <c r="K27" s="13" t="n">
-        <v>299</v>
+        <v>4048.7</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>310</v>
+        <v>4135.5</v>
       </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
@@ -5016,53 +4086,53 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>808.55</v>
+        <v>223.35</v>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22 10:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23 15:00</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>772.5</v>
+        <v>221.8</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-23 10:15</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>821.75</v>
+        <v>225</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-26 09:15</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>5.99% (49.25)</t>
+          <t>1.42% (3.2)</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>871</v>
+        <v>228.2</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>920.25</v>
+        <v>231.4</v>
       </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
@@ -5078,53 +4148,53 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>1300.2</v>
+        <v>1100.3</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>2026-10-22 09:30</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1296.7</v>
+        <v>1094</v>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-22 09:15</t>
+          <t>2026-10-26 11:15</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1314</v>
+        <v>1158.5</v>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>2026-10-21 15:15</t>
+          <t>2026-10-26 10:00</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>1.32% (17.3)</t>
+          <t>5.57% (64.5)</t>
         </is>
       </c>
       <c r="K29" s="13" t="n">
-        <v>1331.3</v>
+        <v>1223</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1348.6</v>
+        <v>1287.5</v>
       </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
@@ -5132,936 +4202,6 @@
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>402.1</v>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>395.75</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>407.5</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>2.88% (11.75)</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>431</v>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>2843.4</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>2828.2</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>2889.1</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>2.11% (60.9)</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>2950</v>
-      </c>
-      <c r="L31" s="13" t="n">
-        <v>3010.9</v>
-      </c>
-      <c r="M31" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N31" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>1814.4</v>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 14:45</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1781.1</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1834.9</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>2.93% (53.8)</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>1888.7</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>1942.5</v>
-      </c>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>256.95</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:00</t>
-        </is>
-      </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:00</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n">
-        <v>254.85</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:45</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>257.05</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:15</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>0.86% (2.2)</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="L33" s="13" t="n">
-        <v>261.45</v>
-      </c>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N33" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>1003.5</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>1001.4</v>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:30</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>1028</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>2.59% (26.6)</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>1054.6</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>1081.2</v>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>11125</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:45</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="n">
-        <v>10990</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>11200</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-21 15:15</t>
-        </is>
-      </c>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>1.88% (210.0)</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>11410</v>
-      </c>
-      <c r="L35" s="13" t="n">
-        <v>11620</v>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N35" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>152.77</v>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:00</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:30</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>152.4</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22 12:15</t>
-        </is>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>155.43</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 11:00</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>1.95% (3.03)</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>158.46</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>161.49</v>
-      </c>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>245</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 14:45</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>242.3</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:00</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>248.4</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>2.46% (6.1)</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>254.5</v>
-      </c>
-      <c r="L37" s="13" t="n">
-        <v>260.6</v>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N37" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>953.2</v>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:15</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="n">
-        <v>948.9</v>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:30</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>961.4</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>1.3% (12.5)</t>
-        </is>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>973.9</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>986.4</v>
-      </c>
-      <c r="M38" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>8937.5</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:15</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>8797.5</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>8946.5</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:15</t>
-        </is>
-      </c>
-      <c r="J39" s="11" t="inlineStr">
-        <is>
-          <t>1.67% (149.0)</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>9095.5</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>9244.5</v>
-      </c>
-      <c r="M39" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N39" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>7008.5</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:15</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 15:00</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>6918</v>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:15</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>7084.5</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:15</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>2.35% (166.5)</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>7251</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>7417.5</v>
-      </c>
-      <c r="M40" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>GODREJCP</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:45</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>837.3</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:15</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>846</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:30</t>
-        </is>
-      </c>
-      <c r="J41" s="11" t="inlineStr">
-        <is>
-          <t>1.03% (8.7)</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>854.7</v>
-      </c>
-      <c r="L41" s="13" t="n">
-        <v>863.4</v>
-      </c>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N41" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>857.15</v>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:00</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:15</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>852</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 10:30</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>889.8</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 14:30</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>4.25% (37.8)</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>927.6</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>965.4</v>
-      </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>1636.2</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 09:45</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-23 14:15</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>1605.1</v>
-      </c>
-      <c r="G43" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 13:15</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>1694</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-22 15:00</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>5.25% (88.9)</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>1782.9</v>
-      </c>
-      <c r="L43" s="13" t="n">
-        <v>1871.8</v>
-      </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N43" s="11" t="inlineStr">
-        <is>
-          <t>Setup Matched</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>340.7</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>340.4</v>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-23 12:45</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>345.25</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-23 11:00</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>1.4% (4.85)</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>350.1</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>354.95</v>
-      </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
@@ -716,35 +716,35 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2447.8</v>
+        <v>2433.4</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 13:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2481</v>
+        <v>2492.8</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 12:30</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>1.34% (33.2)</t>
+          <t>2.38% (59.4)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2514.2</v>
+        <v>2552.2</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2547.4</v>
+        <v>2611.6</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1150,35 +1150,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>2026-10-27 11:45</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>683.85</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>688.3</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
           <t>2026-10-26 15:00</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>684</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:45</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>690</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:15</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.87% (6.0)</t>
+          <t>0.65% (4.45)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>696</v>
+        <v>692.75</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>702</v>
+        <v>697.2</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -1336,35 +1336,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 15:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>73.22</v>
+        <v>73.19</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 14:15</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>74.84999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 10:45</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.18% (1.63)</t>
+          <t>1.67% (1.24)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>76.48</v>
+        <v>75.67</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>78.11</v>
+        <v>76.91</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 11:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1906,23 +1906,23 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>313.9</v>
+        <v>314.45</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 11:15</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.08% (3.4)</t>
+          <t>1.26% (3.95)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>317.3</v>
+        <v>318.4</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>320.7</v>
+        <v>322.35</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 11:30</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2364,6 +2364,502 @@
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1166.5</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:30</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>4.15% (48.4)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1263.3</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>10834</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>10735</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>10856</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:45</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>1.11% (121.0)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>10977</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>11098</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1415</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (37.6)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1490.2</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1527.8</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>1.39% (5.0)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>999.7</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>1014.8</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:30</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (15.1)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1029.9</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>1045</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1758.2</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1818.6</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:15</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>3.32% (60.4)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1879</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1939.4</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>440.25</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:45</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>0.74% (3.25)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>1227</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>1241.5</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>1.17% (14.5)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2380,7 +2876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2541,7 +3037,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C3" s="13" t="n">
@@ -2554,35 +3050,35 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2447.8</v>
+        <v>2433.4</v>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 13:30</t>
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2481</v>
+        <v>2492.8</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 12:30</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr">
         <is>
-          <t>1.34% (33.2)</t>
+          <t>2.38% (59.4)</t>
         </is>
       </c>
       <c r="K3" s="13" t="n">
-        <v>2514.2</v>
+        <v>2552.2</v>
       </c>
       <c r="L3" s="13" t="n">
-        <v>2547.4</v>
+        <v>2611.6</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
@@ -2975,7 +3471,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -2988,35 +3484,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
+          <t>2026-10-27 11:45</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>683.85</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>688.3</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
           <t>2026-10-26 15:00</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
-        <v>684</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:45</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>690</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>2026-10-26 13:15</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.87% (6.0)</t>
+          <t>0.65% (4.45)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>696</v>
+        <v>692.75</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>702</v>
+        <v>697.2</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -3161,7 +3657,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -3174,35 +3670,35 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 15:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>73.22</v>
+        <v>73.19</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 14:15</t>
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>74.84999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 10:45</t>
         </is>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>2.18% (1.63)</t>
+          <t>1.67% (1.24)</t>
         </is>
       </c>
       <c r="K13" s="13" t="n">
-        <v>76.48</v>
+        <v>75.67</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>78.11</v>
+        <v>76.91</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
@@ -3732,7 +4228,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 11:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -3744,23 +4240,23 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>313.9</v>
+        <v>314.45</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-27 11:15</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.08% (3.4)</t>
+          <t>1.26% (3.95)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>317.3</v>
+        <v>318.4</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>320.7</v>
+        <v>322.35</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -3918,7 +4414,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 11:30</t>
+          <t>2026-10-27 14:30</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -4202,6 +4698,502 @@
         </is>
       </c>
       <c r="N29" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1118.1</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1166.5</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:30</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>4.15% (48.4)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1214.9</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>1263.3</v>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>10834</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>10735</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>10856</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:45</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>1.11% (121.0)</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>10977</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>11098</v>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>1415</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>1452.6</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 10:15</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2.59% (37.6)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>1490.2</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>1527.8</v>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>354.3</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:30</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>359.3</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:15</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>1.39% (5.0)</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>364.3</v>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>369.3</v>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>1002.8</v>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>999.7</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:30</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>1014.8</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:30</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>1.49% (15.1)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>1029.9</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>1045</v>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>1781.1</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1758.2</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1818.6</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 15:15</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>3.32% (60.4)</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>1879</v>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1939.4</v>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>437.45</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>437</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:00</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>440.25</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:45</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>0.74% (3.25)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>443.5</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>446.75</v>
+      </c>
+      <c r="M36" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>1227</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>1241.5</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>1.17% (14.5)</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>1270.5</v>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,12 +542,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
@@ -840,35 +840,35 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 11:45</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>906.55</v>
+        <v>900.05</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>920.6</v>
+        <v>913.05</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 15:00</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>1.53% (14.05)</t>
+          <t>1.42% (13.0)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>934.65</v>
+        <v>926.05</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>948.7</v>
+        <v>939.05</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -964,35 +964,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4507.9</v>
+        <v>4500</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4540.1</v>
+        <v>4564</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 15:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>1.4% (64.0)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4572.3</v>
+        <v>4628</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>4604.5</v>
+        <v>4692</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15</t>
+          <t>2026-10-28 10:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1398,35 +1398,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>254.5</v>
+        <v>252.85</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 10:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>256.25</v>
+        <v>255.9</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>1.19% (3.05)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>258</v>
+        <v>258.95</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>259.75</v>
+        <v>262</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -1708,35 +1708,35 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1169.8</v>
+        <v>1139.2</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 14:00</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1188.2</v>
+        <v>1261.4</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 13:00</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>9.69% (122.2)</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1206.6</v>
+        <v>1383.6</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1225</v>
+        <v>1505.8</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -1906,23 +1906,23 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>314.45</v>
+        <v>315.4</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.26% (3.95)</t>
+          <t>1.55% (4.9)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>318.4</v>
+        <v>320.3</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>322.35</v>
+        <v>325.2</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 15:00</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>289.5</v>
+        <v>283.7</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 10:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>291.8</v>
+        <v>298.2</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-26 15:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.79% (2.3)</t>
+          <t>4.86% (14.5)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>294.1</v>
+        <v>312.7</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>296.4</v>
+        <v>327.2</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:15</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -2860,6 +2860,564 @@
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1628.2</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>1680</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>3.08% (51.8)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>1731.8</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1783.6</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:30</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>1.62% (8.35)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>525.1</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:45</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>1.91% (26.5)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>1414.4</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>1440.9</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1556.1</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>1583.9</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:45</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>1.76% (27.8)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>1611.7</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1639.5</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:15</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>3930.5</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>4125</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:30</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>4.72% (194.5)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4319.5</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>4514</v>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:45</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>1148</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:30</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>2.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1245.5</v>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>262.35</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.16% (3.05)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>2432.1</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:30</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>2432.4</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>0.99% (24.2)</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>2456.6</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>1738.33</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>1734.9</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>1811.4</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>4.22% (76.5)</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>1887.9</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>1964.4</v>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -2876,12 +3434,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -3050,7 +3608,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 12:30</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -3112,7 +3670,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:45</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
@@ -3161,7 +3719,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
@@ -3174,35 +3732,35 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 11:45</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
-        <v>906.55</v>
+        <v>900.05</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>920.6</v>
+        <v>913.05</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 15:00</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>1.53% (14.05)</t>
+          <t>1.42% (13.0)</t>
         </is>
       </c>
       <c r="K5" s="13" t="n">
-        <v>934.65</v>
+        <v>926.05</v>
       </c>
       <c r="L5" s="13" t="n">
-        <v>948.7</v>
+        <v>939.05</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -3285,7 +3843,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -3298,35 +3856,35 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4507.9</v>
+        <v>4500</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4540.1</v>
+        <v>4564</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 15:15</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0.71% (32.2)</t>
+          <t>1.4% (64.0)</t>
         </is>
       </c>
       <c r="K7" s="13" t="n">
-        <v>4572.3</v>
+        <v>4628</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>4604.5</v>
+        <v>4692</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -3670,7 +4228,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 15:15</t>
+          <t>2026-10-28 10:45</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -3719,7 +4277,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -3732,35 +4290,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-28 11:15</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>254.5</v>
+        <v>252.85</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 10:15</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>256.25</v>
+        <v>255.9</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-28 09:45</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>0.68% (1.75)</t>
+          <t>1.19% (3.05)</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>258</v>
+        <v>258.95</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>259.75</v>
+        <v>262</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
@@ -4029,7 +4587,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -4042,35 +4600,35 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1169.8</v>
+        <v>1139.2</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 14:00</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1188.2</v>
+        <v>1261.4</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 13:00</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>1.55% (18.4)</t>
+          <t>9.69% (122.2)</t>
         </is>
       </c>
       <c r="K19" s="13" t="n">
-        <v>1206.6</v>
+        <v>1383.6</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1225</v>
+        <v>1505.8</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
@@ -4228,7 +4786,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -4240,23 +4798,23 @@
         </is>
       </c>
       <c r="H22" s="8" t="n">
-        <v>314.45</v>
+        <v>315.4</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 11:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.26% (3.95)</t>
+          <t>1.55% (4.9)</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>318.4</v>
+        <v>320.3</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>322.35</v>
+        <v>325.2</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
@@ -4339,7 +4897,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -4352,35 +4910,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-28 15:00</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>289.5</v>
+        <v>283.7</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-27 10:15</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>291.8</v>
+        <v>298.2</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-26 15:15</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>0.79% (2.3)</t>
+          <t>4.86% (14.5)</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>294.1</v>
+        <v>312.7</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>296.4</v>
+        <v>327.2</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
@@ -4414,7 +4972,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:30</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
@@ -4724,7 +5282,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 15:00</t>
+          <t>2026-10-28 14:15</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -4972,7 +5530,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 14:45</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="F34" s="6" t="n">
@@ -5034,7 +5592,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27 14:15</t>
+          <t>2026-10-28 11:30</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -5194,6 +5752,564 @@
         </is>
       </c>
       <c r="N37" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>1628.2</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>1680</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>3.08% (51.8)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>1731.8</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>1783.6</v>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>511.5</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>508.4</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:30</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>516.75</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>1.62% (8.35)</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>525.1</v>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>533.45</v>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1375.1</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:45</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:00</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>1.91% (26.5)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>1414.4</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>1440.9</v>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1556.1</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:15</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>1583.9</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:45</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr">
+        <is>
+          <t>1.76% (27.8)</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>1611.7</v>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1639.5</v>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>4100</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 15:15</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>3930.5</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>4125</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 12:30</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>4.72% (194.5)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4319.5</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>4514</v>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:45</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>1148</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:30</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1180.5</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>2.75% (32.5)</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>1213</v>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1245.5</v>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>259.3</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:15</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>262.35</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:45</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.16% (3.05)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>265.4</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>268.45</v>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>2432.1</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-28 12:00</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:30</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>2432.4</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>0.99% (24.2)</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>2456.6</v>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>1738.33</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>1734.9</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>1811.4</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-27 15:15</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>4.22% (76.5)</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>1887.9</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>1964.4</v>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -778,35 +778,35 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 11:15</t>
+          <t>2026-10-29 14:30</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2234.3</v>
+        <v>2220</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-29 14:00</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>2283.3</v>
+        <v>2282.3</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-29 11:45</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>2.73% (62.3)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2332.3</v>
+        <v>2344.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2381.3</v>
+        <v>2406.9</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-29 10:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 11:00</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 13:45</t>
+          <t>2026-10-29 11:00</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15</t>
+          <t>2026-10-29 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:45</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -3418,6 +3418,254 @@
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:30</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:00</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>2.02% (8.0)</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>412.7</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>1163.1</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>1168.6</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:45</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (12.4)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>1181</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>1193.4</v>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>827.09</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>810.2</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>832.5</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>2.68% (22.3)</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:45</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:45</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:45</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>348.4</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:45</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>4.28% (14.9)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -3434,7 +3682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3657,7 +3905,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C4" s="5" t="n">
@@ -3670,35 +3918,35 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 11:15</t>
+          <t>2026-10-29 14:30</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>2234.3</v>
+        <v>2220</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-26 09:30</t>
+          <t>2026-10-29 14:00</t>
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>2283.3</v>
+        <v>2282.3</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 09:15</t>
+          <t>2026-10-29 11:45</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.15% (49.0)</t>
+          <t>2.73% (62.3)</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>2332.3</v>
+        <v>2344.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2381.3</v>
+        <v>2406.9</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
@@ -4600,7 +4848,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-29 10:15</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -5840,7 +6088,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 11:00</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -5902,7 +6150,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 13:45</t>
+          <t>2026-10-29 11:00</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -6026,7 +6274,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 15:15</t>
+          <t>2026-10-29 15:00</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -6088,7 +6336,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:45</t>
+          <t>2026-10-29 09:45</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
@@ -6310,6 +6558,254 @@
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:30</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 13:00</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>396.7</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29 12:00</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>2.02% (8.0)</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>404.7</v>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>412.7</v>
+      </c>
+      <c r="M47" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>1163.1</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>1156.2</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>1168.6</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:45</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>1.06% (12.4)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>1181</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>1193.4</v>
+      </c>
+      <c r="M48" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>827.09</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>810.2</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>832.5</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:15</t>
+        </is>
+      </c>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>2.68% (22.3)</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>854.8</v>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>877.1</v>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>340.3</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:45</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:45</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:45</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>348.4</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:45</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>4.28% (14.9)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>363.3</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>378.2</v>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>

--- a/data/weekly_final_trading_signals.xlsx
+++ b/data/weekly_final_trading_signals.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -1150,35 +1150,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 11:45</t>
+          <t>2026-10-30 11:00</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>683.85</v>
+        <v>669.5</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>688.3</v>
+        <v>687.25</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00</t>
+          <t>2026-10-27 12:30</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.65% (4.45)</t>
+          <t>2.58% (17.75)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>692.75</v>
+        <v>705</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>697.2</v>
+        <v>722.75</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:15</t>
+          <t>2026-10-30 12:00</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00</t>
+          <t>2026-10-30 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -3072,35 +3072,35 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1556.1</v>
+        <v>1553.3</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27 14:15</t>
+          <t>2026-10-30 11:45</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1583.9</v>
+        <v>1585.7</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 10:45</t>
+          <t>2026-10-28 15:00</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>1.76% (27.8)</t>
+          <t>2.04% (32.4)</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>1611.7</v>
+        <v>1618.1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>1639.5</v>
+        <v>1650.5</v>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
@@ -3506,35 +3506,35 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1156.2</v>
+        <v>1152.6</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 13:15</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1168.6</v>
+        <v>1164.5</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28 13:45</t>
+          <t>2026-10-30 11:30</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.06% (12.4)</t>
+          <t>1.02% (11.9)</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1181</v>
+        <v>1176.4</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>1193.4</v>
+        <v>1188.3</v>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -3580,23 +3580,23 @@
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>832.5</v>
+        <v>828.25</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2.68% (22.3)</t>
+          <t>2.18% (18.05)</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>854.8</v>
+        <v>846.3</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>877.1</v>
+        <v>864.35</v>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
@@ -3666,6 +3666,68 @@
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>1450.5</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:00</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1342.5</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:30</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>1457</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>7.86% (114.5)</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>1571.5</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>1686</v>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
@@ -3682,7 +3744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4277,7 +4339,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -4290,35 +4352,35 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-27 11:45</t>
+          <t>2026-10-30 11:00</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>683.85</v>
+        <v>669.5</v>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27 09:15</t>
+          <t>2026-10-28 09:15</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>688.3</v>
+        <v>687.25</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2026-10-26 15:00</t>
+          <t>2026-10-27 12:30</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>0.65% (4.45)</t>
+          <t>2.58% (17.75)</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>692.75</v>
+        <v>705</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>697.2</v>
+        <v>722.75</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -4476,7 +4538,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 10:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -4848,7 +4910,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 10:15</t>
+          <t>2026-10-30 12:00</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -5158,7 +5220,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 15:00</t>
+          <t>2026-10-30 09:15</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
@@ -5530,7 +5592,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28 14:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="F30" s="6" t="n">
@@ -6088,7 +6150,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 09:45</t>
+          <t>2026-10-30 10:15</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -6199,7 +6261,7 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -6212,35 +6274,35 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>2026-10-28 14:30</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1556.1</v>
+        <v>1553.3</v>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27 14:15</t>
+          <t>2026-10-30 11:45</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1583.9</v>
+        <v>1585.7</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>2026-10-27 10:45</t>
+          <t>2026-10-28 15:00</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>1.76% (27.8)</t>
+          <t>2.04% (32.4)</t>
         </is>
       </c>
       <c r="K41" s="13" t="n">
-        <v>1611.7</v>
+        <v>1618.1</v>
       </c>
       <c r="L41" s="13" t="n">
-        <v>1639.5</v>
+        <v>1650.5</v>
       </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
@@ -6633,7 +6695,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
@@ -6646,35 +6708,35 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 15:15</t>
         </is>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1156.2</v>
+        <v>1152.6</v>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 13:15</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1168.6</v>
+        <v>1164.5</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>2026-10-28 13:45</t>
+          <t>2026-10-30 11:30</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.06% (12.4)</t>
+          <t>1.02% (11.9)</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1181</v>
+        <v>1176.4</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>1193.4</v>
+        <v>1188.3</v>
       </c>
       <c r="M48" s="10" t="inlineStr">
         <is>
@@ -6708,7 +6770,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
@@ -6720,23 +6782,23 @@
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>832.5</v>
+        <v>828.25</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>2026-10-29 09:15</t>
+          <t>2026-10-30 14:00</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>2.68% (22.3)</t>
+          <t>2.18% (18.05)</t>
         </is>
       </c>
       <c r="K49" s="13" t="n">
-        <v>854.8</v>
+        <v>846.3</v>
       </c>
       <c r="L49" s="13" t="n">
-        <v>877.1</v>
+        <v>864.35</v>
       </c>
       <c r="M49" s="10" t="inlineStr">
         <is>
@@ -6806,6 +6868,68 @@
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Setup Matched</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>1450.5</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:45</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-30 15:00</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1342.5</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29 09:30</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>1457</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:15</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>7.86% (114.5)</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>1571.5</v>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>1686</v>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr">
         <is>
           <t>Setup Matched</t>
         </is>
